--- a/Financial Analysis/TSLA.xlsx
+++ b/Financial Analysis/TSLA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336B0D79-E2CC-4689-AE9D-272B2FC8383C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50023BCC-D72E-4BF1-8E34-8BF16E0D3423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -833,14 +833,14 @@
         <v>42</v>
       </c>
       <c r="D3" s="14">
-        <v>256.58999999999997</v>
+        <v>348.37</v>
       </c>
       <c r="E3" s="12">
-        <v>45770</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45771</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="12">
         <v>45867</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>826476.3899999999</v>
+        <v>1122099.77</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
@@ -918,7 +918,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>797009.3899999999</v>
+        <v>1092632.77</v>
       </c>
     </row>
   </sheetData>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="BJ36" s="10">
         <f>Main!D3</f>
-        <v>256.58999999999997</v>
+        <v>348.37</v>
       </c>
     </row>
     <row r="37" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="BJ37" s="16">
         <f>BJ35/BJ36-1</f>
-        <v>-0.62575831274388716</v>
+        <v>-0.72435435160017803</v>
       </c>
     </row>
     <row r="38" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.3">

--- a/Financial Analysis/TSLA.xlsx
+++ b/Financial Analysis/TSLA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50023BCC-D72E-4BF1-8E34-8BF16E0D3423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3DAD80-974A-4BF7-9C65-AEC577F697D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
   <si>
     <t>Leasing</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q225 8K</t>
   </si>
 </sst>
 </file>
@@ -833,17 +836,17 @@
         <v>42</v>
       </c>
       <c r="D3" s="14">
-        <v>348.37</v>
+        <v>312.60000000000002</v>
       </c>
       <c r="E3" s="12">
-        <v>45804</v>
+        <v>45862</v>
       </c>
       <c r="F3" s="12">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45899</v>
       </c>
       <c r="G3" s="12">
-        <v>45867</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
@@ -851,11 +854,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
@@ -864,7 +866,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>1122099.77</v>
+        <v>1007509.8</v>
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.3">
@@ -872,11 +874,11 @@
         <v>44</v>
       </c>
       <c r="D6" s="2">
-        <f>16352+20644</f>
-        <v>36996</v>
+        <f>36782</f>
+        <v>36782</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L6">
         <v>2020</v>
@@ -890,11 +892,11 @@
         <v>45</v>
       </c>
       <c r="D7" s="2">
-        <f>2237+5292</f>
-        <v>7529</v>
+        <f>2040+5180</f>
+        <v>7220</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K7" t="s">
         <v>27</v>
@@ -906,7 +908,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>29467</v>
+        <v>29562</v>
       </c>
       <c r="M8" t="s">
         <v>57</v>
@@ -918,7 +920,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>1092632.77</v>
+        <v>977947.8</v>
       </c>
     </row>
   </sheetData>
@@ -1211,16 +1213,15 @@
         <v>12925</v>
       </c>
       <c r="AJ3" s="1">
-        <f>AF3*0.75</f>
-        <v>13897.5</v>
+        <v>15787</v>
       </c>
       <c r="AK3" s="1">
         <f>AG3*0.8</f>
         <v>15064.800000000001</v>
       </c>
       <c r="AL3" s="1">
-        <f>AH3*0.85</f>
-        <v>15860.15</v>
+        <f>AH3*0.88</f>
+        <v>16419.920000000002</v>
       </c>
       <c r="AM3" s="1"/>
       <c r="AO3" s="2">
@@ -1257,47 +1258,47 @@
       </c>
       <c r="AW3" s="2">
         <f>SUM(AI3:AL3)</f>
-        <v>57747.450000000004</v>
+        <v>60196.72</v>
       </c>
       <c r="AX3" s="2">
-        <f>AW3*1.02</f>
-        <v>58902.399000000005</v>
+        <f>AW3*1.15</f>
+        <v>69226.228000000003</v>
       </c>
       <c r="AY3" s="2">
-        <f t="shared" ref="AY3" si="4">AX3*1.02</f>
-        <v>60080.446980000008</v>
+        <f>AX3*1.09</f>
+        <v>75456.588520000005</v>
       </c>
       <c r="AZ3" s="2">
-        <f>AY3*1.02</f>
-        <v>61282.05591960001</v>
+        <f>AY3*1.07</f>
+        <v>80738.549716400012</v>
       </c>
       <c r="BA3" s="2">
-        <f>AZ3*1.02</f>
-        <v>62507.697037992009</v>
+        <f>AZ3*1.05</f>
+        <v>84775.47720222002</v>
       </c>
       <c r="BB3" s="2">
-        <f t="shared" ref="BB3:BG3" si="5">BA3*1.01</f>
-        <v>63132.774008371933</v>
+        <f>BA3*1.04</f>
+        <v>88166.496290308816</v>
       </c>
       <c r="BC3" s="2">
-        <f t="shared" si="5"/>
-        <v>63764.101748455651</v>
+        <f>BB3*1.03</f>
+        <v>90811.491179018078</v>
       </c>
       <c r="BD3" s="2">
-        <f t="shared" si="5"/>
-        <v>64401.742765940209</v>
+        <f t="shared" ref="BD3:BG3" si="4">BC3*1.03</f>
+        <v>93535.835914388619</v>
       </c>
       <c r="BE3" s="2">
-        <f t="shared" si="5"/>
-        <v>65045.760193599614</v>
+        <f t="shared" si="4"/>
+        <v>96341.910991820274</v>
       </c>
       <c r="BF3" s="2">
-        <f t="shared" si="5"/>
-        <v>65696.217795535616</v>
+        <f t="shared" si="4"/>
+        <v>99232.168321574878</v>
       </c>
       <c r="BG3" s="2">
-        <f t="shared" si="5"/>
-        <v>66353.179973490973</v>
+        <f t="shared" si="4"/>
+        <v>102209.13337122212</v>
       </c>
     </row>
     <row r="4" spans="2:60" x14ac:dyDescent="0.3">
@@ -1370,16 +1371,15 @@
         <v>595</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" ref="AJ4" si="6">AF4*0.75</f>
-        <v>667.5</v>
+        <v>439</v>
       </c>
       <c r="AK4" s="1">
-        <f t="shared" ref="AK4" si="7">AG4*0.8</f>
-        <v>591.20000000000005</v>
+        <f>AG4*0.75</f>
+        <v>554.25</v>
       </c>
       <c r="AL4" s="1">
-        <f t="shared" ref="AL4" si="8">AH4*0.85</f>
-        <v>588.19999999999993</v>
+        <f t="shared" ref="AL4" si="5">AH4*0.75</f>
+        <v>519</v>
       </c>
       <c r="AM4" s="1"/>
       <c r="AO4" s="2"/>
@@ -1401,47 +1401,47 @@
       </c>
       <c r="AW4" s="2">
         <f>SUM(AI4:AL4)</f>
-        <v>2441.9</v>
+        <v>2107.25</v>
       </c>
       <c r="AX4" s="2">
-        <f>AW4*1.05</f>
-        <v>2563.9950000000003</v>
+        <f>AW4*0.8</f>
+        <v>1685.8000000000002</v>
       </c>
       <c r="AY4" s="2">
-        <f>AX4*1.03</f>
-        <v>2640.9148500000006</v>
+        <f t="shared" ref="AY4:BG4" si="6">AX4*0.8</f>
+        <v>1348.6400000000003</v>
       </c>
       <c r="AZ4" s="2">
-        <f>AY4*1.02</f>
-        <v>2693.7331470000008</v>
+        <f t="shared" si="6"/>
+        <v>1078.9120000000003</v>
       </c>
       <c r="BA4" s="2">
-        <f t="shared" ref="BA4:BG4" si="9">AZ4*1.02</f>
-        <v>2747.6078099400011</v>
+        <f t="shared" si="6"/>
+        <v>863.12960000000021</v>
       </c>
       <c r="BB4" s="2">
-        <f t="shared" si="9"/>
-        <v>2802.559966138801</v>
+        <f t="shared" si="6"/>
+        <v>690.50368000000026</v>
       </c>
       <c r="BC4" s="2">
-        <f t="shared" si="9"/>
-        <v>2858.611165461577</v>
+        <f t="shared" si="6"/>
+        <v>552.40294400000028</v>
       </c>
       <c r="BD4" s="2">
-        <f t="shared" si="9"/>
-        <v>2915.7833887708084</v>
+        <f t="shared" si="6"/>
+        <v>441.92235520000025</v>
       </c>
       <c r="BE4" s="2">
-        <f t="shared" si="9"/>
-        <v>2974.0990565462248</v>
+        <f t="shared" si="6"/>
+        <v>353.5378841600002</v>
       </c>
       <c r="BF4" s="2">
-        <f t="shared" si="9"/>
-        <v>3033.5810376771492</v>
+        <f t="shared" si="6"/>
+        <v>282.83030732800017</v>
       </c>
       <c r="BG4" s="2">
-        <f t="shared" si="9"/>
-        <v>3094.252658430692</v>
+        <f t="shared" si="6"/>
+        <v>226.26424586240014</v>
       </c>
     </row>
     <row r="5" spans="2:60" x14ac:dyDescent="0.3">
@@ -1548,15 +1548,14 @@
         <v>447</v>
       </c>
       <c r="AJ5" s="1">
-        <f t="shared" ref="AJ5:AL5" si="10">AF5*0.95</f>
-        <v>435.09999999999997</v>
+        <v>435</v>
       </c>
       <c r="AK5" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="AK5:AL5" si="7">AG5*0.95</f>
         <v>423.7</v>
       </c>
       <c r="AL5" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
         <v>424.65</v>
       </c>
       <c r="AM5" s="1"/>
@@ -1594,47 +1593,47 @@
       </c>
       <c r="AW5" s="2">
         <f>SUM(AI5:AL5)</f>
-        <v>1730.4499999999998</v>
+        <v>1730.35</v>
       </c>
       <c r="AX5" s="2">
-        <f t="shared" ref="AX5:BG5" si="11">AW5*0.95</f>
-        <v>1643.9274999999998</v>
+        <f t="shared" ref="AX5:BG5" si="8">AW5*0.95</f>
+        <v>1643.8324999999998</v>
       </c>
       <c r="AY5" s="2">
-        <f t="shared" si="11"/>
-        <v>1561.7311249999998</v>
+        <f t="shared" si="8"/>
+        <v>1561.6408749999996</v>
       </c>
       <c r="AZ5" s="2">
-        <f t="shared" si="11"/>
-        <v>1483.6445687499997</v>
+        <f t="shared" si="8"/>
+        <v>1483.5588312499995</v>
       </c>
       <c r="BA5" s="2">
-        <f t="shared" si="11"/>
-        <v>1409.4623403124997</v>
+        <f t="shared" si="8"/>
+        <v>1409.3808896874993</v>
       </c>
       <c r="BB5" s="2">
-        <f t="shared" si="11"/>
-        <v>1338.9892232968746</v>
+        <f t="shared" si="8"/>
+        <v>1338.9118452031244</v>
       </c>
       <c r="BC5" s="2">
-        <f t="shared" si="11"/>
-        <v>1272.0397621320308</v>
+        <f t="shared" si="8"/>
+        <v>1271.9662529429681</v>
       </c>
       <c r="BD5" s="2">
-        <f t="shared" si="11"/>
-        <v>1208.4377740254292</v>
+        <f t="shared" si="8"/>
+        <v>1208.3679402958196</v>
       </c>
       <c r="BE5" s="2">
-        <f t="shared" si="11"/>
-        <v>1148.0158853241578</v>
+        <f t="shared" si="8"/>
+        <v>1147.9495432810286</v>
       </c>
       <c r="BF5" s="2">
-        <f t="shared" si="11"/>
-        <v>1090.6150910579499</v>
+        <f t="shared" si="8"/>
+        <v>1090.5520661169771</v>
       </c>
       <c r="BG5" s="2">
-        <f t="shared" si="11"/>
-        <v>1036.0843365050523</v>
+        <f t="shared" si="8"/>
+        <v>1036.0244628111282</v>
       </c>
     </row>
     <row r="6" spans="2:60" x14ac:dyDescent="0.3">
@@ -1646,222 +1645,222 @@
         <v>2289.5</v>
       </c>
       <c r="D6" s="4">
-        <f t="shared" ref="D6:AL6" si="12">SUM(D3:D5)</f>
+        <f t="shared" ref="D6:AL6" si="9">SUM(D3:D5)</f>
         <v>2286.5</v>
       </c>
       <c r="E6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2362.6999999999998</v>
       </c>
       <c r="F6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2702.1</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>2735.2000000000003</v>
       </c>
       <c r="H6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>3357.6000000000004</v>
       </c>
       <c r="I6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>6098.7</v>
       </c>
       <c r="J6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>6323.0999999999995</v>
       </c>
       <c r="K6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>3724</v>
       </c>
       <c r="L6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>5376</v>
       </c>
       <c r="M6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>5353</v>
       </c>
       <c r="N6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>6368</v>
       </c>
       <c r="O6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>5132</v>
       </c>
       <c r="P6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>5179</v>
       </c>
       <c r="Q6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>7611</v>
       </c>
       <c r="R6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>9314</v>
       </c>
       <c r="S6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>9002</v>
       </c>
       <c r="T6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>10206</v>
       </c>
       <c r="U6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>12057</v>
       </c>
       <c r="V6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>15967</v>
       </c>
       <c r="W6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>16861</v>
       </c>
       <c r="X6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>14602</v>
       </c>
       <c r="Y6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>18692</v>
       </c>
       <c r="Z6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>21307</v>
       </c>
       <c r="AA6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>19963</v>
       </c>
       <c r="AB6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>21268</v>
       </c>
       <c r="AC6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>19625</v>
       </c>
       <c r="AD6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>21563</v>
       </c>
       <c r="AE6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>17378</v>
       </c>
       <c r="AF6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>19878</v>
       </c>
       <c r="AG6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>20016</v>
       </c>
       <c r="AH6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>19798</v>
       </c>
       <c r="AI6" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>13967</v>
       </c>
       <c r="AJ6" s="4">
-        <f t="shared" si="12"/>
-        <v>15000.1</v>
+        <f t="shared" si="9"/>
+        <v>16661</v>
       </c>
       <c r="AK6" s="4">
-        <f t="shared" si="12"/>
-        <v>16079.700000000003</v>
+        <f t="shared" si="9"/>
+        <v>16042.750000000002</v>
       </c>
       <c r="AL6" s="4">
-        <f t="shared" si="12"/>
-        <v>16873</v>
+        <f t="shared" si="9"/>
+        <v>17363.570000000003</v>
       </c>
       <c r="AM6" s="4"/>
       <c r="AN6" s="3"/>
       <c r="AO6" s="4">
-        <f t="shared" ref="AO6" si="13">SUM(AO3:AO5)</f>
+        <f t="shared" ref="AO6" si="10">SUM(AO3:AO5)</f>
         <v>9640.7999999999993</v>
       </c>
       <c r="AP6" s="4">
-        <f t="shared" ref="AP6" si="14">SUM(AP3:AP5)</f>
+        <f t="shared" ref="AP6" si="11">SUM(AP3:AP5)</f>
         <v>18514.600000000002</v>
       </c>
       <c r="AQ6" s="4">
-        <f t="shared" ref="AQ6" si="15">SUM(AQ3:AQ5)</f>
+        <f t="shared" ref="AQ6" si="12">SUM(AQ3:AQ5)</f>
         <v>20821</v>
       </c>
       <c r="AR6" s="4">
-        <f t="shared" ref="AR6" si="16">SUM(AR3:AR5)</f>
+        <f t="shared" ref="AR6" si="13">SUM(AR3:AR5)</f>
         <v>27236</v>
       </c>
       <c r="AS6" s="4">
-        <f t="shared" ref="AS6" si="17">SUM(AS3:AS5)</f>
+        <f t="shared" ref="AS6" si="14">SUM(AS3:AS5)</f>
         <v>46285</v>
       </c>
       <c r="AT6" s="4">
-        <f t="shared" ref="AT6" si="18">SUM(AT3:AT5)</f>
+        <f t="shared" ref="AT6" si="15">SUM(AT3:AT5)</f>
         <v>71462</v>
       </c>
       <c r="AU6" s="4">
-        <f t="shared" ref="AU6" si="19">SUM(AU3:AU5)</f>
+        <f t="shared" ref="AU6" si="16">SUM(AU3:AU5)</f>
         <v>82419</v>
       </c>
       <c r="AV6" s="4">
-        <f t="shared" ref="AV6" si="20">SUM(AV3:AV5)</f>
+        <f t="shared" ref="AV6" si="17">SUM(AV3:AV5)</f>
         <v>77070</v>
       </c>
       <c r="AW6" s="4">
-        <f t="shared" ref="AW6" si="21">SUM(AW3:AW5)</f>
-        <v>61919.8</v>
+        <f t="shared" ref="AW6" si="18">SUM(AW3:AW5)</f>
+        <v>64034.32</v>
       </c>
       <c r="AX6" s="4">
-        <f t="shared" ref="AX6" si="22">SUM(AX3:AX5)</f>
-        <v>63110.321500000005</v>
+        <f t="shared" ref="AX6" si="19">SUM(AX3:AX5)</f>
+        <v>72555.86050000001</v>
       </c>
       <c r="AY6" s="4">
-        <f t="shared" ref="AY6" si="23">SUM(AY3:AY5)</f>
-        <v>64283.092955000007</v>
+        <f t="shared" ref="AY6" si="20">SUM(AY3:AY5)</f>
+        <v>78366.869395000002</v>
       </c>
       <c r="AZ6" s="4">
-        <f t="shared" ref="AZ6" si="24">SUM(AZ3:AZ5)</f>
-        <v>65459.433635350011</v>
+        <f t="shared" ref="AZ6" si="21">SUM(AZ3:AZ5)</f>
+        <v>83301.020547650012</v>
       </c>
       <c r="BA6" s="4">
-        <f t="shared" ref="BA6" si="25">SUM(BA3:BA5)</f>
-        <v>66664.767188244514</v>
+        <f t="shared" ref="BA6" si="22">SUM(BA3:BA5)</f>
+        <v>87047.987691907518</v>
       </c>
       <c r="BB6" s="4">
-        <f t="shared" ref="BB6" si="26">SUM(BB3:BB5)</f>
-        <v>67274.323197807607</v>
+        <f t="shared" ref="BB6" si="23">SUM(BB3:BB5)</f>
+        <v>90195.911815511936</v>
       </c>
       <c r="BC6" s="4">
-        <f t="shared" ref="BC6" si="27">SUM(BC3:BC5)</f>
-        <v>67894.752676049262</v>
+        <f t="shared" ref="BC6" si="24">SUM(BC3:BC5)</f>
+        <v>92635.860375961041</v>
       </c>
       <c r="BD6" s="4">
-        <f t="shared" ref="BD6" si="28">SUM(BD3:BD5)</f>
-        <v>68525.963928736441</v>
+        <f t="shared" ref="BD6" si="25">SUM(BD3:BD5)</f>
+        <v>95186.126209884445</v>
       </c>
       <c r="BE6" s="4">
-        <f t="shared" ref="BE6" si="29">SUM(BE3:BE5)</f>
-        <v>69167.875135469993</v>
+        <f t="shared" ref="BE6" si="26">SUM(BE3:BE5)</f>
+        <v>97843.398419261299</v>
       </c>
       <c r="BF6" s="4">
-        <f t="shared" ref="BF6" si="30">SUM(BF3:BF5)</f>
-        <v>69820.413924270717</v>
+        <f t="shared" ref="BF6" si="27">SUM(BF3:BF5)</f>
+        <v>100605.55069501985</v>
       </c>
       <c r="BG6" s="4">
-        <f t="shared" ref="BG6" si="31">SUM(BG3:BG5)</f>
-        <v>70483.516968426717</v>
+        <f t="shared" ref="BG6" si="28">SUM(BG3:BG5)</f>
+        <v>103471.42207989565</v>
       </c>
     </row>
     <row r="7" spans="2:60" x14ac:dyDescent="0.3">
@@ -1968,8 +1967,7 @@
         <v>2730</v>
       </c>
       <c r="AJ7" s="1">
-        <f>AF7*0.98</f>
-        <v>2953.72</v>
+        <v>2789</v>
       </c>
       <c r="AK7" s="1">
         <f>AG7*1.3</f>
@@ -2013,48 +2011,48 @@
         <v>10086</v>
       </c>
       <c r="AW7" s="2">
-        <f>SUM(AI7:AL7)</f>
-        <v>11925.35</v>
+        <f t="shared" ref="AW7:AW8" si="29">SUM(AI7:AL7)</f>
+        <v>11760.63</v>
       </c>
       <c r="AX7" s="2">
         <f>AW7*1.3</f>
-        <v>15502.955000000002</v>
+        <v>15288.819</v>
       </c>
       <c r="AY7" s="2">
         <f>AX7*1.25</f>
-        <v>19378.693750000002</v>
+        <v>19111.02375</v>
       </c>
       <c r="AZ7" s="2">
         <f>AY7*1.2</f>
-        <v>23254.432500000003</v>
+        <v>22933.228500000001</v>
       </c>
       <c r="BA7" s="2">
         <f>AZ7*1.15</f>
-        <v>26742.597375000001</v>
+        <v>26373.212775</v>
       </c>
       <c r="BB7" s="2">
         <f>BA7*1.1</f>
-        <v>29416.857112500005</v>
+        <v>29010.534052500003</v>
       </c>
       <c r="BC7" s="2">
         <f>BB7*1.05</f>
-        <v>30887.699968125005</v>
+        <v>30461.060755125003</v>
       </c>
       <c r="BD7" s="2">
-        <f t="shared" ref="BD7:BG7" si="32">BC7*1.05</f>
-        <v>32432.084966531256</v>
+        <f t="shared" ref="BD7:BG7" si="30">BC7*1.05</f>
+        <v>31984.113792881253</v>
       </c>
       <c r="BE7" s="2">
-        <f t="shared" si="32"/>
-        <v>34053.689214857819</v>
+        <f t="shared" si="30"/>
+        <v>33583.319482525316</v>
       </c>
       <c r="BF7" s="2">
-        <f t="shared" si="32"/>
-        <v>35756.373675600713</v>
+        <f t="shared" si="30"/>
+        <v>35262.485456651586</v>
       </c>
       <c r="BG7" s="2">
-        <f t="shared" si="32"/>
-        <v>37544.192359380751</v>
+        <f t="shared" si="30"/>
+        <v>37025.609729484167</v>
       </c>
     </row>
     <row r="8" spans="2:60" x14ac:dyDescent="0.3">
@@ -2161,15 +2159,14 @@
         <v>2638</v>
       </c>
       <c r="AJ8" s="1">
-        <f>AF8*1.1</f>
-        <v>2868.8</v>
+        <v>3046</v>
       </c>
       <c r="AK8" s="1">
-        <f t="shared" ref="AK8:AL8" si="33">AG8*1.1</f>
+        <f t="shared" ref="AK8:AL8" si="31">AG8*1.1</f>
         <v>3069.0000000000005</v>
       </c>
       <c r="AL8" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>3132.8</v>
       </c>
       <c r="AM8" s="1"/>
@@ -2206,48 +2203,48 @@
         <v>10534</v>
       </c>
       <c r="AW8" s="2">
-        <f>SUM(AI8:AL8)</f>
-        <v>11708.600000000002</v>
+        <f t="shared" si="29"/>
+        <v>11885.8</v>
       </c>
       <c r="AX8" s="2">
         <f>AW8*1.15</f>
-        <v>13464.890000000001</v>
+        <v>13668.669999999998</v>
       </c>
       <c r="AY8" s="2">
-        <f t="shared" ref="AY8:AZ8" si="34">AX8*1.15</f>
-        <v>15484.6235</v>
+        <f t="shared" ref="AY8:AZ8" si="32">AX8*1.15</f>
+        <v>15718.970499999998</v>
       </c>
       <c r="AZ8" s="2">
-        <f t="shared" si="34"/>
-        <v>17807.317024999997</v>
+        <f t="shared" si="32"/>
+        <v>18076.816074999995</v>
       </c>
       <c r="BA8" s="2">
         <f>AZ8*1.2</f>
-        <v>21368.780429999995</v>
+        <v>21692.179289999993</v>
       </c>
       <c r="BB8" s="2">
-        <f t="shared" ref="BB8:BG8" si="35">BA8*1.2</f>
-        <v>25642.536515999993</v>
+        <f t="shared" ref="BB8:BG8" si="33">BA8*1.2</f>
+        <v>26030.61514799999</v>
       </c>
       <c r="BC8" s="2">
-        <f t="shared" si="35"/>
-        <v>30771.043819199989</v>
+        <f t="shared" si="33"/>
+        <v>31236.738177599986</v>
       </c>
       <c r="BD8" s="2">
-        <f t="shared" si="35"/>
-        <v>36925.252583039983</v>
+        <f t="shared" si="33"/>
+        <v>37484.085813119978</v>
       </c>
       <c r="BE8" s="2">
-        <f t="shared" si="35"/>
-        <v>44310.303099647979</v>
+        <f t="shared" si="33"/>
+        <v>44980.902975743971</v>
       </c>
       <c r="BF8" s="2">
-        <f t="shared" si="35"/>
-        <v>53172.363719577574</v>
+        <f t="shared" si="33"/>
+        <v>53977.083570892763</v>
       </c>
       <c r="BG8" s="2">
-        <f t="shared" si="35"/>
-        <v>63806.836463493084</v>
+        <f t="shared" si="33"/>
+        <v>64772.500285071314</v>
       </c>
     </row>
     <row r="9" spans="2:60" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2259,144 +2256,144 @@
         <v>2696.1</v>
       </c>
       <c r="D9" s="4">
-        <f t="shared" ref="D9:AL9" si="36">SUM(D6:D8)</f>
+        <f t="shared" ref="D9:AL9" si="34">SUM(D6:D8)</f>
         <v>2789.2999999999997</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>2984.3999999999996</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>3288.1</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>3408.6000000000004</v>
       </c>
       <c r="H9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>4001.6000000000004</v>
       </c>
       <c r="I9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>6824.3</v>
       </c>
       <c r="J9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>7225.5999999999995</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>4541</v>
       </c>
       <c r="L9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>6350</v>
       </c>
       <c r="M9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>6303</v>
       </c>
       <c r="N9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>7384</v>
       </c>
       <c r="O9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>5985</v>
       </c>
       <c r="P9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>6036</v>
       </c>
       <c r="Q9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>8771</v>
       </c>
       <c r="R9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>10744</v>
       </c>
       <c r="S9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>10389</v>
       </c>
       <c r="T9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>11958</v>
       </c>
       <c r="U9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>13757</v>
       </c>
       <c r="V9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>17719</v>
       </c>
       <c r="W9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>18756</v>
       </c>
       <c r="X9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>16934</v>
       </c>
       <c r="Y9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>21454</v>
       </c>
       <c r="Z9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>24318</v>
       </c>
       <c r="AA9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>23329</v>
       </c>
       <c r="AB9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>24927</v>
       </c>
       <c r="AC9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>23350</v>
       </c>
       <c r="AD9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>25167</v>
       </c>
       <c r="AE9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>21301</v>
       </c>
       <c r="AF9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>25500</v>
       </c>
       <c r="AG9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>25182</v>
       </c>
       <c r="AH9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>25707</v>
       </c>
       <c r="AI9" s="4">
-        <f t="shared" si="36"/>
+        <f t="shared" si="34"/>
         <v>19335</v>
       </c>
       <c r="AJ9" s="4">
-        <f t="shared" si="36"/>
-        <v>20822.62</v>
+        <f t="shared" si="34"/>
+        <v>22496</v>
       </c>
       <c r="AK9" s="4">
-        <f t="shared" si="36"/>
-        <v>22237.500000000004</v>
+        <f t="shared" si="34"/>
+        <v>22200.550000000003</v>
       </c>
       <c r="AL9" s="4">
-        <f t="shared" si="36"/>
-        <v>23158.63</v>
+        <f t="shared" si="34"/>
+        <v>23649.200000000001</v>
       </c>
       <c r="AM9" s="4"/>
       <c r="AO9" s="6">
@@ -2420,60 +2417,60 @@
         <v>53823</v>
       </c>
       <c r="AT9" s="4">
-        <f t="shared" ref="AT9" si="37">SUM(AT6:AT8)</f>
+        <f t="shared" ref="AT9" si="35">SUM(AT6:AT8)</f>
         <v>81462</v>
       </c>
       <c r="AU9" s="4">
-        <f t="shared" ref="AU9" si="38">SUM(AU6:AU8)</f>
+        <f t="shared" ref="AU9" si="36">SUM(AU6:AU8)</f>
         <v>96773</v>
       </c>
       <c r="AV9" s="4">
-        <f t="shared" ref="AV9" si="39">SUM(AV6:AV8)</f>
+        <f t="shared" ref="AV9" si="37">SUM(AV6:AV8)</f>
         <v>97690</v>
       </c>
       <c r="AW9" s="4">
-        <f t="shared" ref="AW9" si="40">SUM(AW6:AW8)</f>
-        <v>85553.750000000015</v>
+        <f t="shared" ref="AW9" si="38">SUM(AW6:AW8)</f>
+        <v>87680.75</v>
       </c>
       <c r="AX9" s="4">
-        <f t="shared" ref="AX9" si="41">SUM(AX6:AX8)</f>
-        <v>92078.166500000007</v>
+        <f t="shared" ref="AX9" si="39">SUM(AX6:AX8)</f>
+        <v>101513.34950000001</v>
       </c>
       <c r="AY9" s="4">
-        <f t="shared" ref="AY9" si="42">SUM(AY6:AY8)</f>
-        <v>99146.410205000007</v>
+        <f t="shared" ref="AY9" si="40">SUM(AY6:AY8)</f>
+        <v>113196.863645</v>
       </c>
       <c r="AZ9" s="4">
-        <f t="shared" ref="AZ9" si="43">SUM(AZ6:AZ8)</f>
-        <v>106521.18316035002</v>
+        <f t="shared" ref="AZ9" si="41">SUM(AZ6:AZ8)</f>
+        <v>124311.06512265</v>
       </c>
       <c r="BA9" s="4">
-        <f t="shared" ref="BA9" si="44">SUM(BA6:BA8)</f>
-        <v>114776.14499324451</v>
+        <f t="shared" ref="BA9" si="42">SUM(BA6:BA8)</f>
+        <v>135113.37975690753</v>
       </c>
       <c r="BB9" s="4">
-        <f t="shared" ref="BB9" si="45">SUM(BB6:BB8)</f>
-        <v>122333.7168263076</v>
+        <f t="shared" ref="BB9" si="43">SUM(BB6:BB8)</f>
+        <v>145237.06101601192</v>
       </c>
       <c r="BC9" s="4">
-        <f t="shared" ref="BC9" si="46">SUM(BC6:BC8)</f>
-        <v>129553.49646337425</v>
+        <f t="shared" ref="BC9" si="44">SUM(BC6:BC8)</f>
+        <v>154333.65930868604</v>
       </c>
       <c r="BD9" s="4">
-        <f t="shared" ref="BD9" si="47">SUM(BD6:BD8)</f>
-        <v>137883.30147830769</v>
+        <f t="shared" ref="BD9" si="45">SUM(BD6:BD8)</f>
+        <v>164654.32581588568</v>
       </c>
       <c r="BE9" s="4">
-        <f t="shared" ref="BE9" si="48">SUM(BE6:BE8)</f>
-        <v>147531.86744997581</v>
+        <f t="shared" ref="BE9" si="46">SUM(BE6:BE8)</f>
+        <v>176407.6208775306</v>
       </c>
       <c r="BF9" s="4">
-        <f t="shared" ref="BF9" si="49">SUM(BF6:BF8)</f>
-        <v>158749.15131944901</v>
+        <f t="shared" ref="BF9" si="47">SUM(BF6:BF8)</f>
+        <v>189845.11972256418</v>
       </c>
       <c r="BG9" s="4">
-        <f t="shared" ref="BG9" si="50">SUM(BG6:BG8)</f>
-        <v>171834.54579130057</v>
+        <f t="shared" ref="BG9" si="48">SUM(BG6:BG8)</f>
+        <v>205269.53209445113</v>
       </c>
       <c r="BH9" s="6"/>
     </row>
@@ -2581,16 +2578,15 @@
         <v>11461</v>
       </c>
       <c r="AJ10" s="1">
-        <f>AJ3*0.89</f>
-        <v>12368.775</v>
+        <v>13567</v>
       </c>
       <c r="AK10" s="1">
-        <f t="shared" ref="AK10:AL10" si="51">AK3*0.89</f>
+        <f t="shared" ref="AK10" si="49">AK3*0.89</f>
         <v>13407.672</v>
       </c>
       <c r="AL10" s="1">
-        <f t="shared" si="51"/>
-        <v>14115.5335</v>
+        <f>AL3*0.87</f>
+        <v>14285.330400000001</v>
       </c>
       <c r="AM10" s="1"/>
       <c r="AO10" s="2">
@@ -2606,7 +2602,7 @@
         <v>15939</v>
       </c>
       <c r="AR10" s="2">
-        <f t="shared" ref="AR10:AR26" si="52">O10+P10+Q10+R10</f>
+        <f t="shared" ref="AR10:AR26" si="50">O10+P10+Q10+R10</f>
         <v>19696</v>
       </c>
       <c r="AS10" s="2">
@@ -2626,48 +2622,48 @@
         <v>61870</v>
       </c>
       <c r="AW10" s="2">
-        <f t="shared" ref="AW10:AW13" si="53">SUM(AI10:AL10)</f>
-        <v>51352.980499999998</v>
+        <f t="shared" ref="AW10:AW13" si="51">SUM(AI10:AL10)</f>
+        <v>52721.002399999998</v>
       </c>
       <c r="AX10" s="2">
         <f>AX3*0.84</f>
-        <v>49478.015160000003</v>
+        <v>58150.031519999997</v>
       </c>
       <c r="AY10" s="2">
-        <f t="shared" ref="AY10" si="54">AY3*0.84</f>
-        <v>50467.575463200003</v>
+        <f t="shared" ref="AY10" si="52">AY3*0.84</f>
+        <v>63383.534356800003</v>
       </c>
       <c r="AZ10" s="2">
         <f>AZ3*0.83</f>
-        <v>50864.106413268004</v>
+        <v>67012.996264612011</v>
       </c>
       <c r="BA10" s="2">
         <f>BA3*0.83</f>
-        <v>51881.388541533364</v>
+        <v>70363.646077842612</v>
       </c>
       <c r="BB10" s="2">
         <f>BB3*0.82</f>
-        <v>51768.874686864983</v>
+        <v>72296.526958053219</v>
       </c>
       <c r="BC10" s="2">
         <f>BC3*0.82</f>
-        <v>52286.563433733631</v>
+        <v>74465.422766794814</v>
       </c>
       <c r="BD10" s="2">
         <f>BD3*0.81</f>
-        <v>52165.41164041157</v>
+        <v>75764.027090654781</v>
       </c>
       <c r="BE10" s="2">
         <f>BE3*0.81</f>
-        <v>52687.065756815689</v>
+        <v>78036.947903374428</v>
       </c>
       <c r="BF10" s="2">
         <f>BF3*0.8</f>
-        <v>52556.974236428498</v>
+        <v>79385.734657259905</v>
       </c>
       <c r="BG10" s="2">
         <f>BG3*0.8</f>
-        <v>53082.543978792783</v>
+        <v>81767.306696977699</v>
       </c>
     </row>
     <row r="11" spans="2:60" x14ac:dyDescent="0.3">
@@ -2774,15 +2770,14 @@
         <v>239</v>
       </c>
       <c r="AJ11" s="1">
-        <f t="shared" ref="AJ11:AL11" si="55">AJ5*0.53</f>
-        <v>230.60299999999998</v>
+        <v>228</v>
       </c>
       <c r="AK11" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" ref="AK11:AL11" si="53">AK5*0.53</f>
         <v>224.56100000000001</v>
       </c>
       <c r="AL11" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="53"/>
         <v>225.06450000000001</v>
       </c>
       <c r="AM11" s="1"/>
@@ -2799,7 +2794,7 @@
         <v>459</v>
       </c>
       <c r="AR11" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>563</v>
       </c>
       <c r="AS11" s="2">
@@ -2819,48 +2814,48 @@
         <v>1003</v>
       </c>
       <c r="AW11" s="2">
-        <f t="shared" si="53"/>
-        <v>919.22849999999994</v>
+        <f t="shared" si="51"/>
+        <v>916.6255000000001</v>
       </c>
       <c r="AX11" s="2">
-        <f t="shared" ref="AX11:BG11" si="56">AX5*0.54</f>
-        <v>887.72084999999993</v>
+        <f t="shared" ref="AX11:BG11" si="54">AX5*0.54</f>
+        <v>887.66954999999996</v>
       </c>
       <c r="AY11" s="2">
-        <f t="shared" si="56"/>
-        <v>843.3348074999999</v>
+        <f t="shared" si="54"/>
+        <v>843.28607249999982</v>
       </c>
       <c r="AZ11" s="2">
-        <f t="shared" si="56"/>
-        <v>801.16806712499988</v>
+        <f t="shared" si="54"/>
+        <v>801.12176887499982</v>
       </c>
       <c r="BA11" s="2">
-        <f t="shared" si="56"/>
-        <v>761.1096637687499</v>
+        <f t="shared" si="54"/>
+        <v>761.06568043124969</v>
       </c>
       <c r="BB11" s="2">
-        <f t="shared" si="56"/>
-        <v>723.05418058031228</v>
+        <f t="shared" si="54"/>
+        <v>723.0123964096872</v>
       </c>
       <c r="BC11" s="2">
-        <f t="shared" si="56"/>
-        <v>686.90147155129671</v>
+        <f t="shared" si="54"/>
+        <v>686.8617765892028</v>
       </c>
       <c r="BD11" s="2">
-        <f t="shared" si="56"/>
-        <v>652.5563979737318</v>
+        <f t="shared" si="54"/>
+        <v>652.51868775974265</v>
       </c>
       <c r="BE11" s="2">
-        <f t="shared" si="56"/>
-        <v>619.92857807504527</v>
+        <f t="shared" si="54"/>
+        <v>619.89275337175548</v>
       </c>
       <c r="BF11" s="2">
-        <f t="shared" si="56"/>
-        <v>588.93214917129296</v>
+        <f t="shared" si="54"/>
+        <v>588.89811570316772</v>
       </c>
       <c r="BG11" s="2">
-        <f t="shared" si="56"/>
-        <v>559.48554171272826</v>
+        <f t="shared" si="54"/>
+        <v>559.45320991800929</v>
       </c>
     </row>
     <row r="12" spans="2:60" x14ac:dyDescent="0.3">
@@ -2967,20 +2962,19 @@
         <v>1945</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" ref="AJ12:AL12" si="57">AJ7*0.73</f>
-        <v>2156.2156</v>
+        <v>1943</v>
       </c>
       <c r="AK12" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" ref="AK12:AL12" si="55">AK7*0.73</f>
         <v>2254.8240000000001</v>
       </c>
       <c r="AL12" s="1">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>2301.5659000000001</v>
       </c>
       <c r="AM12" s="1"/>
       <c r="AO12" s="2">
-        <f t="shared" ref="AO12:AO26" si="58">C12+D12+E12+F12</f>
+        <f t="shared" ref="AO12:AO26" si="56">C12+D12+E12+F12</f>
         <v>874.3</v>
       </c>
       <c r="AP12" s="2">
@@ -2992,7 +2986,7 @@
         <v>1341</v>
       </c>
       <c r="AR12" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>1976</v>
       </c>
       <c r="AS12" s="2">
@@ -3012,48 +3006,48 @@
         <v>7446</v>
       </c>
       <c r="AW12" s="2">
-        <f t="shared" si="53"/>
-        <v>8657.6054999999997</v>
+        <f t="shared" si="51"/>
+        <v>8444.3899000000001</v>
       </c>
       <c r="AX12" s="2">
         <f>AX7*0.7</f>
-        <v>10852.068500000001</v>
+        <v>10702.173299999999</v>
       </c>
       <c r="AY12" s="2">
-        <f t="shared" ref="AY12:BG12" si="59">AY7*0.7</f>
-        <v>13565.085625000002</v>
+        <f t="shared" ref="AY12:BG12" si="57">AY7*0.7</f>
+        <v>13377.716624999999</v>
       </c>
       <c r="AZ12" s="2">
-        <f t="shared" si="59"/>
-        <v>16278.10275</v>
+        <f t="shared" si="57"/>
+        <v>16053.25995</v>
       </c>
       <c r="BA12" s="2">
-        <f t="shared" si="59"/>
-        <v>18719.8181625</v>
+        <f t="shared" si="57"/>
+        <v>18461.248942499999</v>
       </c>
       <c r="BB12" s="2">
-        <f t="shared" si="59"/>
-        <v>20591.799978750001</v>
+        <f t="shared" si="57"/>
+        <v>20307.373836750001</v>
       </c>
       <c r="BC12" s="2">
-        <f t="shared" si="59"/>
-        <v>21621.389977687504</v>
+        <f t="shared" si="57"/>
+        <v>21322.7425285875</v>
       </c>
       <c r="BD12" s="2">
-        <f t="shared" si="59"/>
-        <v>22702.459476571879</v>
+        <f t="shared" si="57"/>
+        <v>22388.879655016877</v>
       </c>
       <c r="BE12" s="2">
-        <f t="shared" si="59"/>
-        <v>23837.58245040047</v>
+        <f t="shared" si="57"/>
+        <v>23508.32363776772</v>
       </c>
       <c r="BF12" s="2">
-        <f t="shared" si="59"/>
-        <v>25029.461572920496</v>
+        <f t="shared" si="57"/>
+        <v>24683.739819656108</v>
       </c>
       <c r="BG12" s="2">
-        <f t="shared" si="59"/>
-        <v>26280.934651566524</v>
+        <f t="shared" si="57"/>
+        <v>25917.926810638917</v>
       </c>
     </row>
     <row r="13" spans="2:60" x14ac:dyDescent="0.3">
@@ -3160,20 +3154,19 @@
         <v>2537</v>
       </c>
       <c r="AJ13" s="1">
-        <f t="shared" ref="AJ13:AL13" si="60">AJ8*0.94</f>
-        <v>2696.672</v>
+        <v>2880</v>
       </c>
       <c r="AK13" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" ref="AK13:AL13" si="58">AK8*0.94</f>
         <v>2884.86</v>
       </c>
       <c r="AL13" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>2944.8319999999999</v>
       </c>
       <c r="AM13" s="1"/>
       <c r="AO13" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>1228.8</v>
       </c>
       <c r="AP13" s="2">
@@ -3185,7 +3178,7 @@
         <v>2770</v>
       </c>
       <c r="AR13" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>2671</v>
       </c>
       <c r="AS13" s="2">
@@ -3205,48 +3198,48 @@
         <v>9921</v>
       </c>
       <c r="AW13" s="2">
-        <f t="shared" si="53"/>
-        <v>11063.364000000001</v>
+        <f t="shared" si="51"/>
+        <v>11246.692000000001</v>
       </c>
       <c r="AX13" s="2">
-        <f t="shared" ref="AX13:AZ13" si="61">AX8*0.94</f>
-        <v>12656.9966</v>
+        <f t="shared" ref="AX13:AZ13" si="59">AX8*0.94</f>
+        <v>12848.549799999997</v>
       </c>
       <c r="AY13" s="2">
-        <f t="shared" si="61"/>
-        <v>14555.546089999998</v>
+        <f t="shared" si="59"/>
+        <v>14775.832269999997</v>
       </c>
       <c r="AZ13" s="2">
-        <f t="shared" si="61"/>
-        <v>16738.878003499995</v>
+        <f t="shared" si="59"/>
+        <v>16992.207110499996</v>
       </c>
       <c r="BA13" s="2">
         <f>BA8*0.92</f>
-        <v>19659.277995599998</v>
+        <v>19956.804946799995</v>
       </c>
       <c r="BB13" s="2">
         <f>BB8*0.9</f>
-        <v>23078.282864399993</v>
+        <v>23427.55363319999</v>
       </c>
       <c r="BC13" s="2">
         <f>BC8*0.88</f>
-        <v>27078.518560895991</v>
+        <v>27488.329596287989</v>
       </c>
       <c r="BD13" s="2">
         <f>BD8*0.87</f>
-        <v>32124.969747244784</v>
+        <v>32611.154657414379</v>
       </c>
       <c r="BE13" s="2">
         <f>BE8*0.86</f>
-        <v>38106.860665697262</v>
+        <v>38683.576559139816</v>
       </c>
       <c r="BF13" s="2">
         <f>BF8*0.85</f>
-        <v>45196.509161640934</v>
+        <v>45880.521035258847</v>
       </c>
       <c r="BG13" s="2">
         <f>BG8*0.85</f>
-        <v>54235.81099396912</v>
+        <v>55056.625242310613</v>
       </c>
     </row>
     <row r="14" spans="2:60" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3254,152 +3247,152 @@
         <v>9</v>
       </c>
       <c r="C14" s="4">
-        <f t="shared" ref="C14:E14" si="62">C10+C11+C12+C13</f>
+        <f t="shared" ref="C14:E14" si="60">C10+C11+C12+C13</f>
         <v>2028.1</v>
       </c>
       <c r="D14" s="4">
+        <f t="shared" si="60"/>
+        <v>2122.7000000000003</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="60"/>
+        <v>2535.4</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" ref="F14:I14" si="61">F10+F11+F12+F13</f>
+        <v>2849.2999999999997</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="61"/>
+        <v>2951.9000000000005</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="61"/>
+        <v>3383.1</v>
+      </c>
+      <c r="I14" s="4">
+        <f t="shared" si="61"/>
+        <v>5300.4999999999991</v>
+      </c>
+      <c r="J14" s="4">
+        <f t="shared" ref="J14:T14" si="62">J10+J11+J12+J13</f>
+        <v>5782.9</v>
+      </c>
+      <c r="K14" s="4">
         <f t="shared" si="62"/>
-        <v>2122.7000000000003</v>
-      </c>
-      <c r="E14" s="4">
+        <v>3975</v>
+      </c>
+      <c r="L14" s="4">
         <f t="shared" si="62"/>
-        <v>2535.4</v>
-      </c>
-      <c r="F14" s="4">
-        <f t="shared" ref="F14:I14" si="63">F10+F11+F12+F13</f>
-        <v>2849.2999999999997</v>
-      </c>
-      <c r="G14" s="4">
+        <v>5429</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="62"/>
+        <v>5112</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="62"/>
+        <v>5993</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="62"/>
+        <v>4751</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="62"/>
+        <v>4769</v>
+      </c>
+      <c r="Q14" s="4">
+        <f t="shared" si="62"/>
+        <v>6708</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="62"/>
+        <v>8678</v>
+      </c>
+      <c r="S14" s="4">
+        <f t="shared" si="62"/>
+        <v>8174</v>
+      </c>
+      <c r="T14" s="4">
+        <f t="shared" si="62"/>
+        <v>9074</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" ref="U14:V14" si="63">U10+U11+U12+U13</f>
+        <v>10097</v>
+      </c>
+      <c r="V14" s="4">
         <f t="shared" si="63"/>
-        <v>2951.9000000000005</v>
-      </c>
-      <c r="H14" s="4">
-        <f t="shared" si="63"/>
-        <v>3383.1</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="63"/>
-        <v>5300.4999999999991</v>
-      </c>
-      <c r="J14" s="4">
-        <f t="shared" ref="J14:T14" si="64">J10+J11+J12+J13</f>
-        <v>5782.9</v>
-      </c>
-      <c r="K14" s="4">
-        <f t="shared" si="64"/>
-        <v>3975</v>
-      </c>
-      <c r="L14" s="4">
-        <f t="shared" si="64"/>
-        <v>5429</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="64"/>
-        <v>5112</v>
-      </c>
-      <c r="N14" s="4">
-        <f t="shared" si="64"/>
-        <v>5993</v>
-      </c>
-      <c r="O14" s="4">
-        <f t="shared" si="64"/>
-        <v>4751</v>
-      </c>
-      <c r="P14" s="4">
-        <f t="shared" si="64"/>
-        <v>4769</v>
-      </c>
-      <c r="Q14" s="4">
-        <f t="shared" si="64"/>
-        <v>6708</v>
-      </c>
-      <c r="R14" s="4">
-        <f t="shared" si="64"/>
-        <v>8678</v>
-      </c>
-      <c r="S14" s="4">
-        <f t="shared" si="64"/>
-        <v>8174</v>
-      </c>
-      <c r="T14" s="4">
-        <f t="shared" si="64"/>
-        <v>9074</v>
-      </c>
-      <c r="U14" s="4">
-        <f t="shared" ref="U14:V14" si="65">U10+U11+U12+U13</f>
-        <v>10097</v>
-      </c>
-      <c r="V14" s="4">
-        <f t="shared" si="65"/>
         <v>12872</v>
       </c>
       <c r="W14" s="4">
-        <f t="shared" ref="W14" si="66">W10+W11+W12+W13</f>
+        <f t="shared" ref="W14" si="64">W10+W11+W12+W13</f>
         <v>13296</v>
       </c>
       <c r="X14" s="4">
-        <f t="shared" ref="X14" si="67">X10+X11+X12+X13</f>
+        <f t="shared" ref="X14" si="65">X10+X11+X12+X13</f>
         <v>12700</v>
       </c>
       <c r="Y14" s="4">
-        <f t="shared" ref="Y14" si="68">Y10+Y11+Y12+Y13</f>
+        <f t="shared" ref="Y14" si="66">Y10+Y11+Y12+Y13</f>
         <v>16072</v>
       </c>
       <c r="Z14" s="4">
-        <f t="shared" ref="Z14" si="69">Z10+Z11+Z12+Z13</f>
+        <f t="shared" ref="Z14" si="67">Z10+Z11+Z12+Z13</f>
         <v>18541</v>
       </c>
       <c r="AA14" s="4">
-        <f t="shared" ref="AA14" si="70">AA10+AA11+AA12+AA13</f>
+        <f t="shared" ref="AA14" si="68">AA10+AA11+AA12+AA13</f>
         <v>18818</v>
       </c>
       <c r="AB14" s="4">
-        <f t="shared" ref="AB14:AC14" si="71">AB10+AB11+AB12+AB13</f>
+        <f t="shared" ref="AB14:AC14" si="69">AB10+AB11+AB12+AB13</f>
         <v>20394</v>
       </c>
       <c r="AC14" s="4">
+        <f t="shared" si="69"/>
+        <v>19172</v>
+      </c>
+      <c r="AD14" s="4">
+        <f t="shared" ref="AD14:AE14" si="70">AD10+AD11+AD12+AD13</f>
+        <v>20729</v>
+      </c>
+      <c r="AE14" s="4">
+        <f t="shared" si="70"/>
+        <v>17605</v>
+      </c>
+      <c r="AF14" s="4">
+        <f t="shared" ref="AF14:AH14" si="71">AF10+AF11+AF12+AF13</f>
+        <v>20922</v>
+      </c>
+      <c r="AG14" s="4">
         <f t="shared" si="71"/>
-        <v>19172</v>
-      </c>
-      <c r="AD14" s="4">
-        <f t="shared" ref="AD14:AE14" si="72">AD10+AD11+AD12+AD13</f>
-        <v>20729</v>
-      </c>
-      <c r="AE14" s="4">
+        <v>20185</v>
+      </c>
+      <c r="AH14" s="4">
+        <f t="shared" si="71"/>
+        <v>21528</v>
+      </c>
+      <c r="AI14" s="4">
+        <f t="shared" ref="AI14:AL14" si="72">AI10+AI11+AI12+AI13</f>
+        <v>16182</v>
+      </c>
+      <c r="AJ14" s="4">
         <f t="shared" si="72"/>
-        <v>17605</v>
-      </c>
-      <c r="AF14" s="4">
-        <f t="shared" ref="AF14:AH14" si="73">AF10+AF11+AF12+AF13</f>
-        <v>20922</v>
-      </c>
-      <c r="AG14" s="4">
-        <f t="shared" si="73"/>
-        <v>20185</v>
-      </c>
-      <c r="AH14" s="4">
-        <f t="shared" si="73"/>
-        <v>21528</v>
-      </c>
-      <c r="AI14" s="4">
-        <f t="shared" ref="AI14:AL14" si="74">AI10+AI11+AI12+AI13</f>
-        <v>16182</v>
-      </c>
-      <c r="AJ14" s="4">
-        <f t="shared" si="74"/>
-        <v>17452.265599999999</v>
+        <v>18618</v>
       </c>
       <c r="AK14" s="4">
-        <f t="shared" si="74"/>
+        <f t="shared" si="72"/>
         <v>18771.917000000001</v>
       </c>
       <c r="AL14" s="4">
-        <f t="shared" si="74"/>
-        <v>19586.995899999998</v>
+        <f t="shared" si="72"/>
+        <v>19756.792799999999</v>
       </c>
       <c r="AM14" s="4"/>
       <c r="AO14" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>9535.5</v>
       </c>
       <c r="AP14" s="6">
@@ -3411,7 +3404,7 @@
         <v>20509</v>
       </c>
       <c r="AR14" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>24906</v>
       </c>
       <c r="AS14" s="6">
@@ -3431,48 +3424,48 @@
         <v>80240</v>
       </c>
       <c r="AW14" s="6">
-        <f t="shared" ref="AW14:BG14" si="75">SUM(AW10:AW13)</f>
-        <v>71993.178499999995</v>
+        <f t="shared" ref="AW14:BG14" si="73">SUM(AW10:AW13)</f>
+        <v>73328.709799999997</v>
       </c>
       <c r="AX14" s="6">
-        <f t="shared" si="75"/>
-        <v>73874.80111</v>
+        <f t="shared" si="73"/>
+        <v>82588.424169999984</v>
       </c>
       <c r="AY14" s="6">
-        <f t="shared" si="75"/>
-        <v>79431.541985700009</v>
+        <f t="shared" si="73"/>
+        <v>92380.369324300002</v>
       </c>
       <c r="AZ14" s="6">
-        <f t="shared" si="75"/>
-        <v>84682.255233892996</v>
+        <f t="shared" si="73"/>
+        <v>100859.585093987</v>
       </c>
       <c r="BA14" s="6">
-        <f t="shared" si="75"/>
-        <v>91021.594363402124</v>
+        <f t="shared" si="73"/>
+        <v>109542.76564757385</v>
       </c>
       <c r="BB14" s="6">
-        <f t="shared" si="75"/>
-        <v>96162.011710595296</v>
+        <f t="shared" si="73"/>
+        <v>116754.4668244129</v>
       </c>
       <c r="BC14" s="6">
-        <f t="shared" si="75"/>
-        <v>101673.37344386842</v>
+        <f t="shared" si="73"/>
+        <v>123963.3566682595</v>
       </c>
       <c r="BD14" s="6">
-        <f t="shared" si="75"/>
-        <v>107645.39726220196</v>
+        <f t="shared" si="73"/>
+        <v>131416.58009084579</v>
       </c>
       <c r="BE14" s="6">
-        <f t="shared" si="75"/>
-        <v>115251.43745098845</v>
+        <f t="shared" si="73"/>
+        <v>140848.74085365373</v>
       </c>
       <c r="BF14" s="6">
-        <f t="shared" si="75"/>
-        <v>123371.87712016121</v>
+        <f t="shared" si="73"/>
+        <v>150538.89362787805</v>
       </c>
       <c r="BG14" s="6">
-        <f t="shared" si="75"/>
-        <v>134158.77516604116</v>
+        <f t="shared" si="73"/>
+        <v>163301.31195984525</v>
       </c>
     </row>
     <row r="15" spans="2:60" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3480,148 +3473,148 @@
         <v>16</v>
       </c>
       <c r="C15" s="4">
-        <f t="shared" ref="C15:E15" si="76">C9-C14</f>
+        <f t="shared" ref="C15:E15" si="74">C9-C14</f>
         <v>668</v>
       </c>
       <c r="D15" s="4">
+        <f t="shared" si="74"/>
+        <v>666.59999999999945</v>
+      </c>
+      <c r="E15" s="4">
+        <f t="shared" si="74"/>
+        <v>448.99999999999955</v>
+      </c>
+      <c r="F15" s="4">
+        <f t="shared" ref="F15:I15" si="75">F9-F14</f>
+        <v>438.80000000000018</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="75"/>
+        <v>456.69999999999982</v>
+      </c>
+      <c r="H15" s="4">
+        <f t="shared" si="75"/>
+        <v>618.50000000000045</v>
+      </c>
+      <c r="I15" s="4">
+        <f t="shared" si="75"/>
+        <v>1523.8000000000011</v>
+      </c>
+      <c r="J15" s="4">
+        <f t="shared" ref="J15:T15" si="76">J9-J14</f>
+        <v>1442.6999999999998</v>
+      </c>
+      <c r="K15" s="4">
         <f t="shared" si="76"/>
-        <v>666.59999999999945</v>
-      </c>
-      <c r="E15" s="4">
+        <v>566</v>
+      </c>
+      <c r="L15" s="4">
         <f t="shared" si="76"/>
-        <v>448.99999999999955</v>
-      </c>
-      <c r="F15" s="4">
-        <f t="shared" ref="F15:I15" si="77">F9-F14</f>
-        <v>438.80000000000018</v>
-      </c>
-      <c r="G15" s="4">
+        <v>921</v>
+      </c>
+      <c r="M15" s="4">
+        <f t="shared" si="76"/>
+        <v>1191</v>
+      </c>
+      <c r="N15" s="4">
+        <f t="shared" si="76"/>
+        <v>1391</v>
+      </c>
+      <c r="O15" s="4">
+        <f t="shared" si="76"/>
+        <v>1234</v>
+      </c>
+      <c r="P15" s="4">
+        <f t="shared" si="76"/>
+        <v>1267</v>
+      </c>
+      <c r="Q15" s="4">
+        <f t="shared" si="76"/>
+        <v>2063</v>
+      </c>
+      <c r="R15" s="4">
+        <f t="shared" si="76"/>
+        <v>2066</v>
+      </c>
+      <c r="S15" s="4">
+        <f t="shared" si="76"/>
+        <v>2215</v>
+      </c>
+      <c r="T15" s="4">
+        <f t="shared" si="76"/>
+        <v>2884</v>
+      </c>
+      <c r="U15" s="4">
+        <f t="shared" ref="U15:V15" si="77">U9-U14</f>
+        <v>3660</v>
+      </c>
+      <c r="V15" s="4">
         <f t="shared" si="77"/>
-        <v>456.69999999999982</v>
-      </c>
-      <c r="H15" s="4">
-        <f t="shared" si="77"/>
-        <v>618.50000000000045</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="77"/>
-        <v>1523.8000000000011</v>
-      </c>
-      <c r="J15" s="4">
-        <f t="shared" ref="J15:T15" si="78">J9-J14</f>
-        <v>1442.6999999999998</v>
-      </c>
-      <c r="K15" s="4">
-        <f t="shared" si="78"/>
-        <v>566</v>
-      </c>
-      <c r="L15" s="4">
-        <f t="shared" si="78"/>
-        <v>921</v>
-      </c>
-      <c r="M15" s="4">
-        <f t="shared" si="78"/>
-        <v>1191</v>
-      </c>
-      <c r="N15" s="4">
-        <f t="shared" si="78"/>
-        <v>1391</v>
-      </c>
-      <c r="O15" s="4">
-        <f t="shared" si="78"/>
-        <v>1234</v>
-      </c>
-      <c r="P15" s="4">
-        <f t="shared" si="78"/>
-        <v>1267</v>
-      </c>
-      <c r="Q15" s="4">
-        <f t="shared" si="78"/>
-        <v>2063</v>
-      </c>
-      <c r="R15" s="4">
-        <f t="shared" si="78"/>
-        <v>2066</v>
-      </c>
-      <c r="S15" s="4">
-        <f t="shared" si="78"/>
-        <v>2215</v>
-      </c>
-      <c r="T15" s="4">
-        <f t="shared" si="78"/>
-        <v>2884</v>
-      </c>
-      <c r="U15" s="4">
-        <f t="shared" ref="U15:V15" si="79">U9-U14</f>
-        <v>3660</v>
-      </c>
-      <c r="V15" s="4">
-        <f t="shared" si="79"/>
         <v>4847</v>
       </c>
       <c r="W15" s="4">
-        <f t="shared" ref="W15" si="80">W9-W14</f>
+        <f t="shared" ref="W15" si="78">W9-W14</f>
         <v>5460</v>
       </c>
       <c r="X15" s="4">
-        <f t="shared" ref="X15" si="81">X9-X14</f>
+        <f t="shared" ref="X15" si="79">X9-X14</f>
         <v>4234</v>
       </c>
       <c r="Y15" s="4">
-        <f t="shared" ref="Y15" si="82">Y9-Y14</f>
+        <f t="shared" ref="Y15" si="80">Y9-Y14</f>
         <v>5382</v>
       </c>
       <c r="Z15" s="4">
-        <f t="shared" ref="Z15" si="83">Z9-Z14</f>
+        <f t="shared" ref="Z15" si="81">Z9-Z14</f>
         <v>5777</v>
       </c>
       <c r="AA15" s="4">
-        <f t="shared" ref="AA15" si="84">AA9-AA14</f>
+        <f t="shared" ref="AA15" si="82">AA9-AA14</f>
         <v>4511</v>
       </c>
       <c r="AB15" s="4">
-        <f t="shared" ref="AB15:AC15" si="85">AB9-AB14</f>
+        <f t="shared" ref="AB15:AC15" si="83">AB9-AB14</f>
         <v>4533</v>
       </c>
       <c r="AC15" s="4">
+        <f t="shared" si="83"/>
+        <v>4178</v>
+      </c>
+      <c r="AD15" s="4">
+        <f t="shared" ref="AD15:AE15" si="84">AD9-AD14</f>
+        <v>4438</v>
+      </c>
+      <c r="AE15" s="4">
+        <f t="shared" si="84"/>
+        <v>3696</v>
+      </c>
+      <c r="AF15" s="4">
+        <f t="shared" ref="AF15:AH15" si="85">AF9-AF14</f>
+        <v>4578</v>
+      </c>
+      <c r="AG15" s="4">
         <f t="shared" si="85"/>
-        <v>4178</v>
-      </c>
-      <c r="AD15" s="4">
-        <f t="shared" ref="AD15:AE15" si="86">AD9-AD14</f>
-        <v>4438</v>
-      </c>
-      <c r="AE15" s="4">
+        <v>4997</v>
+      </c>
+      <c r="AH15" s="4">
+        <f t="shared" si="85"/>
+        <v>4179</v>
+      </c>
+      <c r="AI15" s="4">
+        <f t="shared" ref="AI15:AL15" si="86">AI9-AI14</f>
+        <v>3153</v>
+      </c>
+      <c r="AJ15" s="4">
         <f t="shared" si="86"/>
-        <v>3696</v>
-      </c>
-      <c r="AF15" s="4">
-        <f t="shared" ref="AF15:AH15" si="87">AF9-AF14</f>
-        <v>4578</v>
-      </c>
-      <c r="AG15" s="4">
-        <f t="shared" si="87"/>
-        <v>4997</v>
-      </c>
-      <c r="AH15" s="4">
-        <f t="shared" si="87"/>
-        <v>4179</v>
-      </c>
-      <c r="AI15" s="4">
-        <f t="shared" ref="AI15:AL15" si="88">AI9-AI14</f>
-        <v>3153</v>
-      </c>
-      <c r="AJ15" s="4">
-        <f t="shared" si="88"/>
-        <v>3370.3544000000002</v>
+        <v>3878</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" si="88"/>
-        <v>3465.5830000000024</v>
+        <f t="shared" si="86"/>
+        <v>3428.6330000000016</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" si="88"/>
-        <v>3571.6341000000029</v>
+        <f t="shared" si="86"/>
+        <v>3892.4072000000015</v>
       </c>
       <c r="AM15" s="4"/>
       <c r="AO15" s="6">
@@ -3637,7 +3630,7 @@
         <v>4069</v>
       </c>
       <c r="AR15" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>6630</v>
       </c>
       <c r="AS15" s="6">
@@ -3658,47 +3651,47 @@
       </c>
       <c r="AW15" s="6">
         <f>AW9-AW14</f>
-        <v>13560.57150000002</v>
+        <v>14352.040200000003</v>
       </c>
       <c r="AX15" s="6">
-        <f t="shared" ref="AX15:BG15" si="89">AX9-AX14</f>
-        <v>18203.365390000006</v>
+        <f t="shared" ref="AX15:BG15" si="87">AX9-AX14</f>
+        <v>18924.925330000027</v>
       </c>
       <c r="AY15" s="6">
-        <f t="shared" si="89"/>
-        <v>19714.868219299999</v>
+        <f t="shared" si="87"/>
+        <v>20816.494320700003</v>
       </c>
       <c r="AZ15" s="6">
-        <f t="shared" si="89"/>
-        <v>21838.927926457021</v>
+        <f t="shared" si="87"/>
+        <v>23451.480028663005</v>
       </c>
       <c r="BA15" s="6">
-        <f t="shared" si="89"/>
-        <v>23754.550629842386</v>
+        <f t="shared" si="87"/>
+        <v>25570.614109333677</v>
       </c>
       <c r="BB15" s="6">
-        <f t="shared" si="89"/>
-        <v>26171.705115712306</v>
+        <f t="shared" si="87"/>
+        <v>28482.594191599026</v>
       </c>
       <c r="BC15" s="6">
-        <f t="shared" si="89"/>
-        <v>27880.123019505831</v>
+        <f t="shared" si="87"/>
+        <v>30370.30264042654</v>
       </c>
       <c r="BD15" s="6">
-        <f t="shared" si="89"/>
-        <v>30237.90421610573</v>
+        <f t="shared" si="87"/>
+        <v>33237.745725039887</v>
       </c>
       <c r="BE15" s="6">
-        <f t="shared" si="89"/>
-        <v>32280.429998987354</v>
+        <f t="shared" si="87"/>
+        <v>35558.880023876874</v>
       </c>
       <c r="BF15" s="6">
-        <f t="shared" si="89"/>
-        <v>35377.2741992878</v>
+        <f t="shared" si="87"/>
+        <v>39306.226094686135</v>
       </c>
       <c r="BG15" s="6">
-        <f t="shared" si="89"/>
-        <v>37675.770625259407</v>
+        <f t="shared" si="87"/>
+        <v>41968.220134605886</v>
       </c>
     </row>
     <row r="16" spans="2:60" x14ac:dyDescent="0.3">
@@ -3805,20 +3798,19 @@
         <v>1409</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" ref="AJ16:AK16" si="90">AF16*1.15</f>
-        <v>1235.0999999999999</v>
+        <v>1589</v>
       </c>
       <c r="AK16" s="1">
-        <f t="shared" si="90"/>
-        <v>1194.8499999999999</v>
+        <f>AG16*1.5</f>
+        <v>1558.5</v>
       </c>
       <c r="AL16" s="1">
-        <f>AH16*1.1</f>
-        <v>1403.6000000000001</v>
+        <f>AH16*1.4</f>
+        <v>1786.3999999999999</v>
       </c>
       <c r="AM16" s="1"/>
       <c r="AO16" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>1377.9</v>
       </c>
       <c r="AP16" s="2">
@@ -3830,7 +3822,7 @@
         <v>1343</v>
       </c>
       <c r="AR16" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>1491</v>
       </c>
       <c r="AS16" s="2">
@@ -3850,48 +3842,48 @@
         <v>4540</v>
       </c>
       <c r="AW16" s="2">
-        <f>AV16*1.09</f>
-        <v>4948.6000000000004</v>
+        <f t="shared" ref="AW16:AW18" si="88">SUM(AI16:AL16)</f>
+        <v>6342.9</v>
       </c>
       <c r="AX16" s="2">
         <f>AW16*1.07</f>
-        <v>5295.0020000000004</v>
+        <v>6786.9030000000002</v>
       </c>
       <c r="AY16" s="2">
         <f>AX16*1.05</f>
-        <v>5559.7521000000006</v>
+        <v>7126.2481500000004</v>
       </c>
       <c r="AZ16" s="2">
         <f>AY16*1.04</f>
-        <v>5782.1421840000012</v>
+        <v>7411.2980760000009</v>
       </c>
       <c r="BA16" s="2">
         <f>AZ16*1.03</f>
-        <v>5955.6064495200017</v>
+        <v>7633.637018280001</v>
       </c>
       <c r="BB16" s="2">
-        <f t="shared" ref="BB16:BG16" si="91">BA16*1.03</f>
-        <v>6134.2746430056022</v>
+        <f t="shared" ref="BB16:BG16" si="89">BA16*1.03</f>
+        <v>7862.6461288284008</v>
       </c>
       <c r="BC16" s="2">
-        <f t="shared" si="91"/>
-        <v>6318.3028822957704</v>
+        <f t="shared" si="89"/>
+        <v>8098.5255126932534</v>
       </c>
       <c r="BD16" s="2">
-        <f t="shared" si="91"/>
-        <v>6507.851968764644</v>
+        <f t="shared" si="89"/>
+        <v>8341.4812780740504</v>
       </c>
       <c r="BE16" s="2">
-        <f t="shared" si="91"/>
-        <v>6703.0875278275835</v>
+        <f t="shared" si="89"/>
+        <v>8591.7257164162729</v>
       </c>
       <c r="BF16" s="2">
-        <f t="shared" si="91"/>
-        <v>6904.1801536624107</v>
+        <f t="shared" si="89"/>
+        <v>8849.4774879087618</v>
       </c>
       <c r="BG16" s="2">
-        <f t="shared" si="91"/>
-        <v>7111.3055582722836</v>
+        <f t="shared" si="89"/>
+        <v>9114.9618125460256</v>
       </c>
     </row>
     <row r="17" spans="1:180" x14ac:dyDescent="0.3">
@@ -3998,20 +3990,19 @@
         <v>1251</v>
       </c>
       <c r="AJ17" s="1">
-        <f t="shared" ref="AJ17:AL17" si="92">AJ9*0.05</f>
-        <v>1041.1310000000001</v>
+        <v>1366</v>
       </c>
       <c r="AK17" s="1">
-        <f t="shared" si="92"/>
-        <v>1111.8750000000002</v>
+        <f>AK9*0.06</f>
+        <v>1332.0330000000001</v>
       </c>
       <c r="AL17" s="1">
-        <f t="shared" si="92"/>
-        <v>1157.9315000000001</v>
+        <f t="shared" ref="AL17" si="90">AL9*0.06</f>
+        <v>1418.952</v>
       </c>
       <c r="AM17" s="1"/>
       <c r="AO17" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>2476.1999999999998</v>
       </c>
       <c r="AP17" s="2">
@@ -4023,7 +4014,7 @@
         <v>2646</v>
       </c>
       <c r="AR17" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>3145</v>
       </c>
       <c r="AS17" s="2">
@@ -4043,48 +4034,48 @@
         <v>5150</v>
       </c>
       <c r="AW17" s="2">
-        <f>AW9*0.052</f>
-        <v>4448.795000000001</v>
+        <f t="shared" si="88"/>
+        <v>5367.9850000000006</v>
       </c>
       <c r="AX17" s="2">
-        <f t="shared" ref="AX17:BG17" si="93">AX9*0.052</f>
-        <v>4788.0646580000002</v>
+        <f t="shared" ref="AX17:BG17" si="91">AX9*0.052</f>
+        <v>5278.6941740000002</v>
       </c>
       <c r="AY17" s="2">
-        <f t="shared" si="93"/>
-        <v>5155.6133306600004</v>
+        <f t="shared" si="91"/>
+        <v>5886.2369095399999</v>
       </c>
       <c r="AZ17" s="2">
-        <f t="shared" si="93"/>
-        <v>5539.1015243382008</v>
+        <f t="shared" si="91"/>
+        <v>6464.1753863778004</v>
       </c>
       <c r="BA17" s="2">
-        <f t="shared" si="93"/>
-        <v>5968.3595396487144</v>
+        <f t="shared" si="91"/>
+        <v>7025.8957473591909</v>
       </c>
       <c r="BB17" s="2">
-        <f t="shared" si="93"/>
-        <v>6361.3532749679953</v>
+        <f t="shared" si="91"/>
+        <v>7552.3271728326199</v>
       </c>
       <c r="BC17" s="2">
-        <f t="shared" si="93"/>
-        <v>6736.7818160954603</v>
+        <f t="shared" si="91"/>
+        <v>8025.350284051674</v>
       </c>
       <c r="BD17" s="2">
-        <f t="shared" si="93"/>
-        <v>7169.931676872</v>
+        <f t="shared" si="91"/>
+        <v>8562.0249424260546</v>
       </c>
       <c r="BE17" s="2">
-        <f t="shared" si="93"/>
-        <v>7671.6571073987416</v>
+        <f t="shared" si="91"/>
+        <v>9173.1962856315913</v>
       </c>
       <c r="BF17" s="2">
-        <f t="shared" si="93"/>
-        <v>8254.9558686113487</v>
+        <f t="shared" si="91"/>
+        <v>9871.9462255733361</v>
       </c>
       <c r="BG17" s="2">
-        <f t="shared" si="93"/>
-        <v>8935.3963811476297</v>
+        <f t="shared" si="91"/>
+        <v>10674.015668911459</v>
       </c>
     </row>
     <row r="18" spans="1:180" x14ac:dyDescent="0.3">
@@ -4201,7 +4192,7 @@
       </c>
       <c r="AM18" s="1"/>
       <c r="AO18" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AP18" s="2">
@@ -4213,7 +4204,7 @@
         <v>149</v>
       </c>
       <c r="AR18" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AS18" s="2">
@@ -4233,7 +4224,8 @@
         <v>684</v>
       </c>
       <c r="AW18" s="2">
-        <v>0</v>
+        <f t="shared" si="88"/>
+        <v>94</v>
       </c>
       <c r="AX18" s="2">
         <v>0</v>
@@ -4271,148 +4263,148 @@
         <v>19</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" ref="C19:E19" si="94">C16+C17+C18</f>
+        <f t="shared" ref="C19:E19" si="92">C16+C17+C18</f>
         <v>925.4</v>
       </c>
       <c r="D19" s="4">
+        <f t="shared" si="92"/>
+        <v>907.40000000000009</v>
+      </c>
+      <c r="E19" s="4">
+        <f t="shared" si="92"/>
+        <v>984.5</v>
+      </c>
+      <c r="F19" s="4">
+        <f t="shared" ref="F19:I19" si="93">F16+F17+F18</f>
+        <v>1036.8000000000002</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="93"/>
+        <v>1053.4000000000001</v>
+      </c>
+      <c r="H19" s="4">
+        <f t="shared" si="93"/>
+        <v>1240.2000000000003</v>
+      </c>
+      <c r="I19" s="4">
+        <f t="shared" si="93"/>
+        <v>1106.6999999999998</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" ref="J19:R19" si="94">J16+J17+J18</f>
+        <v>1029.1999999999998</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="94"/>
-        <v>907.40000000000009</v>
-      </c>
-      <c r="E19" s="4">
+        <v>1088</v>
+      </c>
+      <c r="L19" s="4">
         <f t="shared" si="94"/>
-        <v>984.5</v>
-      </c>
-      <c r="F19" s="4">
-        <f t="shared" ref="F19:I19" si="95">F16+F17+F18</f>
-        <v>1036.8000000000002</v>
-      </c>
-      <c r="G19" s="4">
+        <v>1088</v>
+      </c>
+      <c r="M19" s="4">
+        <f t="shared" si="94"/>
+        <v>930</v>
+      </c>
+      <c r="N19" s="4">
+        <f t="shared" si="94"/>
+        <v>1032</v>
+      </c>
+      <c r="O19" s="4">
+        <f t="shared" si="94"/>
+        <v>951</v>
+      </c>
+      <c r="P19" s="4">
+        <f t="shared" si="94"/>
+        <v>940</v>
+      </c>
+      <c r="Q19" s="4">
+        <f t="shared" si="94"/>
+        <v>1254</v>
+      </c>
+      <c r="R19" s="4">
+        <f t="shared" si="94"/>
+        <v>1491</v>
+      </c>
+      <c r="S19" s="4">
+        <f t="shared" ref="S19:U19" si="95">S16+S17+S18</f>
+        <v>1621</v>
+      </c>
+      <c r="T19" s="4">
         <f t="shared" si="95"/>
-        <v>1053.4000000000001</v>
-      </c>
-      <c r="H19" s="4">
+        <v>1572</v>
+      </c>
+      <c r="U19" s="4">
         <f t="shared" si="95"/>
-        <v>1240.2000000000003</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="95"/>
-        <v>1106.6999999999998</v>
-      </c>
-      <c r="J19" s="4">
-        <f t="shared" ref="J19:R19" si="96">J16+J17+J18</f>
-        <v>1029.1999999999998</v>
-      </c>
-      <c r="K19" s="4">
-        <f t="shared" si="96"/>
-        <v>1088</v>
-      </c>
-      <c r="L19" s="4">
-        <f t="shared" si="96"/>
-        <v>1088</v>
-      </c>
-      <c r="M19" s="4">
-        <f t="shared" si="96"/>
-        <v>930</v>
-      </c>
-      <c r="N19" s="4">
-        <f t="shared" si="96"/>
-        <v>1032</v>
-      </c>
-      <c r="O19" s="4">
-        <f t="shared" si="96"/>
-        <v>951</v>
-      </c>
-      <c r="P19" s="4">
-        <f t="shared" si="96"/>
-        <v>940</v>
-      </c>
-      <c r="Q19" s="4">
-        <f t="shared" si="96"/>
-        <v>1254</v>
-      </c>
-      <c r="R19" s="4">
-        <f t="shared" si="96"/>
-        <v>1491</v>
-      </c>
-      <c r="S19" s="4">
-        <f t="shared" ref="S19:U19" si="97">S16+S17+S18</f>
-        <v>1621</v>
-      </c>
-      <c r="T19" s="4">
-        <f t="shared" si="97"/>
-        <v>1572</v>
-      </c>
-      <c r="U19" s="4">
-        <f t="shared" si="97"/>
         <v>1656</v>
       </c>
       <c r="V19" s="4">
-        <f t="shared" ref="V19" si="98">V16+V17+V18</f>
+        <f t="shared" ref="V19" si="96">V16+V17+V18</f>
         <v>2234</v>
       </c>
       <c r="W19" s="4">
-        <f t="shared" ref="W19" si="99">W16+W17+W18</f>
+        <f t="shared" ref="W19" si="97">W16+W17+W18</f>
         <v>1857</v>
       </c>
       <c r="X19" s="4">
-        <f t="shared" ref="X19" si="100">X16+X17+X18</f>
+        <f t="shared" ref="X19" si="98">X16+X17+X18</f>
         <v>1770</v>
       </c>
       <c r="Y19" s="4">
-        <f t="shared" ref="Y19" si="101">Y16+Y17+Y18</f>
+        <f t="shared" ref="Y19" si="99">Y16+Y17+Y18</f>
         <v>1694</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" ref="Z19" si="102">Z16+Z17+Z18</f>
+        <f t="shared" ref="Z19" si="100">Z16+Z17+Z18</f>
         <v>1876</v>
       </c>
       <c r="AA19" s="4">
-        <f t="shared" ref="AA19" si="103">AA16+AA17+AA18</f>
+        <f t="shared" ref="AA19" si="101">AA16+AA17+AA18</f>
         <v>1847</v>
       </c>
       <c r="AB19" s="4">
-        <f t="shared" ref="AB19:AC19" si="104">AB16+AB17+AB18</f>
+        <f t="shared" ref="AB19:AC19" si="102">AB16+AB17+AB18</f>
         <v>2134</v>
       </c>
       <c r="AC19" s="4">
+        <f t="shared" si="102"/>
+        <v>2414</v>
+      </c>
+      <c r="AD19" s="4">
+        <f t="shared" ref="AD19:AE19" si="103">AD16+AD17+AD18</f>
+        <v>2374</v>
+      </c>
+      <c r="AE19" s="4">
+        <f t="shared" si="103"/>
+        <v>2525</v>
+      </c>
+      <c r="AF19" s="4">
+        <f t="shared" ref="AF19:AH19" si="104">AF16+AF17+AF18</f>
+        <v>2973</v>
+      </c>
+      <c r="AG19" s="4">
         <f t="shared" si="104"/>
-        <v>2414</v>
-      </c>
-      <c r="AD19" s="4">
-        <f t="shared" ref="AD19:AE19" si="105">AD16+AD17+AD18</f>
-        <v>2374</v>
-      </c>
-      <c r="AE19" s="4">
+        <v>2280</v>
+      </c>
+      <c r="AH19" s="4">
+        <f t="shared" si="104"/>
+        <v>2596</v>
+      </c>
+      <c r="AI19" s="4">
+        <f t="shared" ref="AI19:AL19" si="105">AI16+AI17+AI18</f>
+        <v>2754</v>
+      </c>
+      <c r="AJ19" s="4">
         <f t="shared" si="105"/>
-        <v>2525</v>
-      </c>
-      <c r="AF19" s="4">
-        <f t="shared" ref="AF19:AH19" si="106">AF16+AF17+AF18</f>
-        <v>2973</v>
-      </c>
-      <c r="AG19" s="4">
-        <f t="shared" si="106"/>
-        <v>2280</v>
-      </c>
-      <c r="AH19" s="4">
-        <f t="shared" si="106"/>
-        <v>2596</v>
-      </c>
-      <c r="AI19" s="4">
-        <f t="shared" ref="AI19:AL19" si="107">AI16+AI17+AI18</f>
-        <v>2754</v>
-      </c>
-      <c r="AJ19" s="4">
-        <f t="shared" si="107"/>
-        <v>2276.2309999999998</v>
+        <v>2955</v>
       </c>
       <c r="AK19" s="4">
-        <f t="shared" si="107"/>
-        <v>2306.7250000000004</v>
+        <f t="shared" si="105"/>
+        <v>2890.5330000000004</v>
       </c>
       <c r="AL19" s="4">
-        <f t="shared" si="107"/>
-        <v>2561.5315000000001</v>
+        <f t="shared" si="105"/>
+        <v>3205.3519999999999</v>
       </c>
       <c r="AM19" s="4"/>
       <c r="AO19" s="6">
@@ -4428,68 +4420,68 @@
         <v>4138</v>
       </c>
       <c r="AR19" s="6">
-        <f t="shared" ref="AR19:BB19" si="108">SUM(AR16,AR17,AR18)</f>
+        <f t="shared" ref="AR19:BB19" si="106">SUM(AR16,AR17,AR18)</f>
         <v>4636</v>
       </c>
       <c r="AS19" s="6">
+        <f t="shared" si="106"/>
+        <v>7083</v>
+      </c>
+      <c r="AT19" s="6">
+        <f t="shared" ref="AT19:AU19" si="107">SUM(AT16,AT17,AT18)</f>
+        <v>7197</v>
+      </c>
+      <c r="AU19" s="6">
+        <f t="shared" si="107"/>
+        <v>8769</v>
+      </c>
+      <c r="AV19" s="6">
+        <f t="shared" si="106"/>
+        <v>10374</v>
+      </c>
+      <c r="AW19" s="6">
+        <f t="shared" si="106"/>
+        <v>11804.885</v>
+      </c>
+      <c r="AX19" s="6">
+        <f t="shared" si="106"/>
+        <v>12065.597174</v>
+      </c>
+      <c r="AY19" s="6">
+        <f t="shared" si="106"/>
+        <v>13012.48505954</v>
+      </c>
+      <c r="AZ19" s="6">
+        <f t="shared" si="106"/>
+        <v>13875.473462377802</v>
+      </c>
+      <c r="BA19" s="6">
+        <f t="shared" si="106"/>
+        <v>14659.532765639193</v>
+      </c>
+      <c r="BB19" s="6">
+        <f t="shared" si="106"/>
+        <v>15414.973301661021</v>
+      </c>
+      <c r="BC19" s="6">
+        <f t="shared" ref="BC19:BG19" si="108">SUM(BC16,BC17,BC18)</f>
+        <v>16123.875796744927</v>
+      </c>
+      <c r="BD19" s="6">
         <f t="shared" si="108"/>
-        <v>7083</v>
-      </c>
-      <c r="AT19" s="6">
-        <f t="shared" ref="AT19:AU19" si="109">SUM(AT16,AT17,AT18)</f>
-        <v>7197</v>
-      </c>
-      <c r="AU19" s="6">
-        <f t="shared" si="109"/>
-        <v>8769</v>
-      </c>
-      <c r="AV19" s="6">
+        <v>16903.506220500105</v>
+      </c>
+      <c r="BE19" s="6">
         <f t="shared" si="108"/>
-        <v>10374</v>
-      </c>
-      <c r="AW19" s="6">
+        <v>17764.922002047864</v>
+      </c>
+      <c r="BF19" s="6">
         <f t="shared" si="108"/>
-        <v>9397.3950000000004</v>
-      </c>
-      <c r="AX19" s="6">
+        <v>18721.423713482098</v>
+      </c>
+      <c r="BG19" s="6">
         <f t="shared" si="108"/>
-        <v>10083.066658</v>
-      </c>
-      <c r="AY19" s="6">
-        <f t="shared" si="108"/>
-        <v>10715.36543066</v>
-      </c>
-      <c r="AZ19" s="6">
-        <f t="shared" si="108"/>
-        <v>11321.243708338203</v>
-      </c>
-      <c r="BA19" s="6">
-        <f t="shared" si="108"/>
-        <v>11923.965989168715</v>
-      </c>
-      <c r="BB19" s="6">
-        <f t="shared" si="108"/>
-        <v>12495.627917973598</v>
-      </c>
-      <c r="BC19" s="6">
-        <f t="shared" ref="BC19:BG19" si="110">SUM(BC16,BC17,BC18)</f>
-        <v>13055.084698391231</v>
-      </c>
-      <c r="BD19" s="6">
-        <f t="shared" si="110"/>
-        <v>13677.783645636644</v>
-      </c>
-      <c r="BE19" s="6">
-        <f t="shared" si="110"/>
-        <v>14374.744635226325</v>
-      </c>
-      <c r="BF19" s="6">
-        <f t="shared" si="110"/>
-        <v>15159.13602227376</v>
-      </c>
-      <c r="BG19" s="6">
-        <f t="shared" si="110"/>
-        <v>16046.701939419912</v>
+        <v>19788.977481457485</v>
       </c>
     </row>
     <row r="20" spans="1:180" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -4497,148 +4489,148 @@
         <v>18</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" ref="C20:E20" si="111">C15-C19</f>
+        <f t="shared" ref="C20:E20" si="109">C15-C19</f>
         <v>-257.39999999999998</v>
       </c>
       <c r="D20" s="4">
+        <f t="shared" si="109"/>
+        <v>-240.80000000000064</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="109"/>
+        <v>-535.50000000000045</v>
+      </c>
+      <c r="F20" s="4">
+        <f t="shared" ref="F20:I20" si="110">F15-F19</f>
+        <v>-598</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="110"/>
+        <v>-596.70000000000027</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" si="110"/>
+        <v>-621.69999999999982</v>
+      </c>
+      <c r="I20" s="4">
+        <f t="shared" si="110"/>
+        <v>417.10000000000127</v>
+      </c>
+      <c r="J20" s="4">
+        <f t="shared" ref="J20:R20" si="111">J15-J19</f>
+        <v>413.5</v>
+      </c>
+      <c r="K20" s="4">
         <f t="shared" si="111"/>
-        <v>-240.80000000000064</v>
-      </c>
-      <c r="E20" s="4">
+        <v>-522</v>
+      </c>
+      <c r="L20" s="4">
         <f t="shared" si="111"/>
-        <v>-535.50000000000045</v>
-      </c>
-      <c r="F20" s="4">
-        <f t="shared" ref="F20:I20" si="112">F15-F19</f>
-        <v>-598</v>
-      </c>
-      <c r="G20" s="4">
+        <v>-167</v>
+      </c>
+      <c r="M20" s="4">
+        <f t="shared" si="111"/>
+        <v>261</v>
+      </c>
+      <c r="N20" s="4">
+        <f t="shared" si="111"/>
+        <v>359</v>
+      </c>
+      <c r="O20" s="4">
+        <f t="shared" si="111"/>
+        <v>283</v>
+      </c>
+      <c r="P20" s="4">
+        <f t="shared" si="111"/>
+        <v>327</v>
+      </c>
+      <c r="Q20" s="4">
+        <f t="shared" si="111"/>
+        <v>809</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="111"/>
+        <v>575</v>
+      </c>
+      <c r="S20" s="4">
+        <f t="shared" ref="S20:U20" si="112">S15-S19</f>
+        <v>594</v>
+      </c>
+      <c r="T20" s="4">
         <f t="shared" si="112"/>
-        <v>-596.70000000000027</v>
-      </c>
-      <c r="H20" s="4">
+        <v>1312</v>
+      </c>
+      <c r="U20" s="4">
         <f t="shared" si="112"/>
-        <v>-621.69999999999982</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="112"/>
-        <v>417.10000000000127</v>
-      </c>
-      <c r="J20" s="4">
-        <f t="shared" ref="J20:R20" si="113">J15-J19</f>
-        <v>413.5</v>
-      </c>
-      <c r="K20" s="4">
-        <f t="shared" si="113"/>
-        <v>-522</v>
-      </c>
-      <c r="L20" s="4">
-        <f t="shared" si="113"/>
-        <v>-167</v>
-      </c>
-      <c r="M20" s="4">
-        <f t="shared" si="113"/>
-        <v>261</v>
-      </c>
-      <c r="N20" s="4">
-        <f t="shared" si="113"/>
-        <v>359</v>
-      </c>
-      <c r="O20" s="4">
-        <f t="shared" si="113"/>
-        <v>283</v>
-      </c>
-      <c r="P20" s="4">
-        <f t="shared" si="113"/>
-        <v>327</v>
-      </c>
-      <c r="Q20" s="4">
-        <f t="shared" si="113"/>
-        <v>809</v>
-      </c>
-      <c r="R20" s="4">
-        <f t="shared" si="113"/>
-        <v>575</v>
-      </c>
-      <c r="S20" s="4">
-        <f t="shared" ref="S20:U20" si="114">S15-S19</f>
-        <v>594</v>
-      </c>
-      <c r="T20" s="4">
-        <f t="shared" si="114"/>
-        <v>1312</v>
-      </c>
-      <c r="U20" s="4">
-        <f t="shared" si="114"/>
         <v>2004</v>
       </c>
       <c r="V20" s="4">
-        <f t="shared" ref="V20" si="115">V15-V19</f>
+        <f t="shared" ref="V20" si="113">V15-V19</f>
         <v>2613</v>
       </c>
       <c r="W20" s="4">
-        <f t="shared" ref="W20" si="116">W15-W19</f>
+        <f t="shared" ref="W20" si="114">W15-W19</f>
         <v>3603</v>
       </c>
       <c r="X20" s="4">
-        <f t="shared" ref="X20" si="117">X15-X19</f>
+        <f t="shared" ref="X20" si="115">X15-X19</f>
         <v>2464</v>
       </c>
       <c r="Y20" s="4">
-        <f t="shared" ref="Y20" si="118">Y15-Y19</f>
+        <f t="shared" ref="Y20" si="116">Y15-Y19</f>
         <v>3688</v>
       </c>
       <c r="Z20" s="4">
-        <f t="shared" ref="Z20" si="119">Z15-Z19</f>
+        <f t="shared" ref="Z20" si="117">Z15-Z19</f>
         <v>3901</v>
       </c>
       <c r="AA20" s="4">
-        <f t="shared" ref="AA20" si="120">AA15-AA19</f>
+        <f t="shared" ref="AA20" si="118">AA15-AA19</f>
         <v>2664</v>
       </c>
       <c r="AB20" s="4">
-        <f t="shared" ref="AB20:AC20" si="121">AB15-AB19</f>
+        <f t="shared" ref="AB20:AC20" si="119">AB15-AB19</f>
         <v>2399</v>
       </c>
       <c r="AC20" s="4">
+        <f t="shared" si="119"/>
+        <v>1764</v>
+      </c>
+      <c r="AD20" s="4">
+        <f t="shared" ref="AD20:AE20" si="120">AD15-AD19</f>
+        <v>2064</v>
+      </c>
+      <c r="AE20" s="4">
+        <f t="shared" si="120"/>
+        <v>1171</v>
+      </c>
+      <c r="AF20" s="4">
+        <f t="shared" ref="AF20:AH20" si="121">AF15-AF19</f>
+        <v>1605</v>
+      </c>
+      <c r="AG20" s="4">
         <f t="shared" si="121"/>
-        <v>1764</v>
-      </c>
-      <c r="AD20" s="4">
-        <f t="shared" ref="AD20:AE20" si="122">AD15-AD19</f>
-        <v>2064</v>
-      </c>
-      <c r="AE20" s="4">
+        <v>2717</v>
+      </c>
+      <c r="AH20" s="4">
+        <f t="shared" si="121"/>
+        <v>1583</v>
+      </c>
+      <c r="AI20" s="4">
+        <f t="shared" ref="AI20:AL20" si="122">AI15-AI19</f>
+        <v>399</v>
+      </c>
+      <c r="AJ20" s="4">
         <f t="shared" si="122"/>
-        <v>1171</v>
-      </c>
-      <c r="AF20" s="4">
-        <f t="shared" ref="AF20:AH20" si="123">AF15-AF19</f>
-        <v>1605</v>
-      </c>
-      <c r="AG20" s="4">
-        <f t="shared" si="123"/>
-        <v>2717</v>
-      </c>
-      <c r="AH20" s="4">
-        <f t="shared" si="123"/>
-        <v>1583</v>
-      </c>
-      <c r="AI20" s="4">
-        <f t="shared" ref="AI20:AL20" si="124">AI15-AI19</f>
-        <v>399</v>
-      </c>
-      <c r="AJ20" s="4">
-        <f t="shared" si="124"/>
-        <v>1094.1234000000004</v>
+        <v>923</v>
       </c>
       <c r="AK20" s="4">
-        <f t="shared" si="124"/>
-        <v>1158.858000000002</v>
+        <f t="shared" si="122"/>
+        <v>538.10000000000127</v>
       </c>
       <c r="AL20" s="4">
-        <f t="shared" si="124"/>
-        <v>1010.1026000000029</v>
+        <f t="shared" si="122"/>
+        <v>687.05520000000161</v>
       </c>
       <c r="AM20" s="4"/>
       <c r="AO20" s="6">
@@ -4650,72 +4642,72 @@
         <v>-387.80000000000291</v>
       </c>
       <c r="AQ20" s="6">
-        <f t="shared" ref="AQ20:BB20" si="125">AQ15-AQ19</f>
+        <f t="shared" ref="AQ20:BB20" si="123">AQ15-AQ19</f>
         <v>-69</v>
       </c>
       <c r="AR20" s="6">
+        <f t="shared" si="123"/>
+        <v>1994</v>
+      </c>
+      <c r="AS20" s="6">
+        <f t="shared" si="123"/>
+        <v>6523</v>
+      </c>
+      <c r="AT20" s="6">
+        <f t="shared" ref="AT20:AU20" si="124">AT15-AT19</f>
+        <v>13656</v>
+      </c>
+      <c r="AU20" s="6">
+        <f t="shared" si="124"/>
+        <v>8891</v>
+      </c>
+      <c r="AV20" s="6">
+        <f t="shared" si="123"/>
+        <v>7076</v>
+      </c>
+      <c r="AW20" s="6">
+        <f t="shared" si="123"/>
+        <v>2547.1552000000029</v>
+      </c>
+      <c r="AX20" s="6">
+        <f t="shared" si="123"/>
+        <v>6859.3281560000269</v>
+      </c>
+      <c r="AY20" s="6">
+        <f t="shared" si="123"/>
+        <v>7804.009261160003</v>
+      </c>
+      <c r="AZ20" s="6">
+        <f t="shared" si="123"/>
+        <v>9576.006566285203</v>
+      </c>
+      <c r="BA20" s="6">
+        <f t="shared" si="123"/>
+        <v>10911.081343694485</v>
+      </c>
+      <c r="BB20" s="6">
+        <f t="shared" si="123"/>
+        <v>13067.620889938005</v>
+      </c>
+      <c r="BC20" s="6">
+        <f t="shared" ref="BC20:BG20" si="125">BC15-BC19</f>
+        <v>14246.426843681613</v>
+      </c>
+      <c r="BD20" s="6">
         <f t="shared" si="125"/>
-        <v>1994</v>
-      </c>
-      <c r="AS20" s="6">
+        <v>16334.239504539783</v>
+      </c>
+      <c r="BE20" s="6">
         <f t="shared" si="125"/>
-        <v>6523</v>
-      </c>
-      <c r="AT20" s="6">
-        <f t="shared" ref="AT20:AU20" si="126">AT15-AT19</f>
-        <v>13656</v>
-      </c>
-      <c r="AU20" s="6">
-        <f t="shared" si="126"/>
-        <v>8891</v>
-      </c>
-      <c r="AV20" s="6">
+        <v>17793.95802182901</v>
+      </c>
+      <c r="BF20" s="6">
         <f t="shared" si="125"/>
-        <v>7076</v>
-      </c>
-      <c r="AW20" s="6">
+        <v>20584.802381204037</v>
+      </c>
+      <c r="BG20" s="6">
         <f t="shared" si="125"/>
-        <v>4163.1765000000196</v>
-      </c>
-      <c r="AX20" s="6">
-        <f t="shared" si="125"/>
-        <v>8120.2987320000066</v>
-      </c>
-      <c r="AY20" s="6">
-        <f t="shared" si="125"/>
-        <v>8999.5027886399985</v>
-      </c>
-      <c r="AZ20" s="6">
-        <f t="shared" si="125"/>
-        <v>10517.684218118819</v>
-      </c>
-      <c r="BA20" s="6">
-        <f t="shared" si="125"/>
-        <v>11830.584640673671</v>
-      </c>
-      <c r="BB20" s="6">
-        <f t="shared" si="125"/>
-        <v>13676.077197738708</v>
-      </c>
-      <c r="BC20" s="6">
-        <f t="shared" ref="BC20:BG20" si="127">BC15-BC19</f>
-        <v>14825.0383211146</v>
-      </c>
-      <c r="BD20" s="6">
-        <f t="shared" si="127"/>
-        <v>16560.120570469087</v>
-      </c>
-      <c r="BE20" s="6">
-        <f t="shared" si="127"/>
-        <v>17905.685363761029</v>
-      </c>
-      <c r="BF20" s="6">
-        <f t="shared" si="127"/>
-        <v>20218.13817701404</v>
-      </c>
-      <c r="BG20" s="6">
-        <f t="shared" si="127"/>
-        <v>21629.068685839495</v>
+        <v>22179.242653148402</v>
       </c>
     </row>
     <row r="21" spans="1:180" x14ac:dyDescent="0.3">
@@ -4822,20 +4814,19 @@
         <v>-400</v>
       </c>
       <c r="AJ21" s="1">
-        <f t="shared" ref="AJ21:AL22" si="128">AF21*1.03</f>
-        <v>-358.44</v>
+        <v>-392</v>
       </c>
       <c r="AK21" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" ref="AK21:AL22" si="126">AG21*1.03</f>
         <v>-441.87</v>
       </c>
       <c r="AL21" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-455.26</v>
       </c>
       <c r="AM21" s="1"/>
       <c r="AO21" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-19.399999999999999</v>
       </c>
       <c r="AP21" s="2">
@@ -4847,7 +4838,7 @@
         <v>-44</v>
       </c>
       <c r="AR21" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>-30</v>
       </c>
       <c r="AS21" s="2">
@@ -4867,48 +4858,48 @@
         <v>-1569</v>
       </c>
       <c r="AW21" s="2">
-        <f t="shared" ref="AW21:AX21" si="129">AV21*1.2</f>
-        <v>-1882.8</v>
+        <f t="shared" ref="AW21:AW23" si="127">SUM(AI21:AL21)</f>
+        <v>-1689.1299999999999</v>
       </c>
       <c r="AX21" s="2">
-        <f t="shared" si="129"/>
-        <v>-2259.3599999999997</v>
+        <f t="shared" ref="AX21" si="128">AW21*1.2</f>
+        <v>-2026.9559999999997</v>
       </c>
       <c r="AY21" s="2">
         <f>AX21*1.01</f>
-        <v>-2281.9535999999998</v>
+        <v>-2047.2255599999996</v>
       </c>
       <c r="AZ21" s="2">
-        <f t="shared" ref="AZ21:BB21" si="130">AY21*1.01</f>
-        <v>-2304.7731359999998</v>
+        <f t="shared" ref="AZ21:BB21" si="129">AY21*1.01</f>
+        <v>-2067.6978155999996</v>
       </c>
       <c r="BA21" s="2">
-        <f t="shared" si="130"/>
-        <v>-2327.8208673599997</v>
+        <f t="shared" si="129"/>
+        <v>-2088.3747937559997</v>
       </c>
       <c r="BB21" s="2">
-        <f t="shared" si="130"/>
-        <v>-2351.0990760335999</v>
+        <f t="shared" si="129"/>
+        <v>-2109.2585416935599</v>
       </c>
       <c r="BC21" s="2">
-        <f t="shared" ref="BC21" si="131">BB21*1.01</f>
-        <v>-2374.6100667939359</v>
+        <f t="shared" ref="BC21" si="130">BB21*1.01</f>
+        <v>-2130.3511271104953</v>
       </c>
       <c r="BD21" s="2">
-        <f t="shared" ref="BD21" si="132">BC21*1.01</f>
-        <v>-2398.3561674618754</v>
+        <f t="shared" ref="BD21" si="131">BC21*1.01</f>
+        <v>-2151.6546383816003</v>
       </c>
       <c r="BE21" s="2">
-        <f t="shared" ref="BE21" si="133">BD21*1.01</f>
-        <v>-2422.339729136494</v>
+        <f t="shared" ref="BE21" si="132">BD21*1.01</f>
+        <v>-2173.1711847654165</v>
       </c>
       <c r="BF21" s="2">
-        <f t="shared" ref="BF21" si="134">BE21*1.01</f>
-        <v>-2446.5631264278591</v>
+        <f t="shared" ref="BF21" si="133">BE21*1.01</f>
+        <v>-2194.9028966130704</v>
       </c>
       <c r="BG21" s="2">
-        <f t="shared" ref="BG21" si="135">BF21*1.01</f>
-        <v>-2471.0287576921378</v>
+        <f t="shared" ref="BG21" si="134">BF21*1.01</f>
+        <v>-2216.8519255792012</v>
       </c>
     </row>
     <row r="22" spans="1:180" x14ac:dyDescent="0.3">
@@ -5015,20 +5006,19 @@
         <v>91</v>
       </c>
       <c r="AJ22" s="1">
-        <f t="shared" si="128"/>
-        <v>88.58</v>
+        <v>86</v>
       </c>
       <c r="AK22" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>94.76</v>
       </c>
       <c r="AL22" s="1">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>98.88</v>
       </c>
       <c r="AM22" s="1"/>
       <c r="AO22" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>471.09999999999997</v>
       </c>
       <c r="AP22" s="2">
@@ -5040,7 +5030,7 @@
         <v>685</v>
       </c>
       <c r="AR22" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>748</v>
       </c>
       <c r="AS22" s="2">
@@ -5060,48 +5050,48 @@
         <v>350</v>
       </c>
       <c r="AW22" s="2">
-        <f t="shared" ref="AW22:BB22" si="136">AV22*0.9</f>
-        <v>315</v>
+        <f t="shared" si="127"/>
+        <v>370.64</v>
       </c>
       <c r="AX22" s="2">
+        <f t="shared" ref="AX22:BB22" si="135">AW22*0.9</f>
+        <v>333.57600000000002</v>
+      </c>
+      <c r="AY22" s="2">
+        <f t="shared" si="135"/>
+        <v>300.21840000000003</v>
+      </c>
+      <c r="AZ22" s="2">
+        <f t="shared" si="135"/>
+        <v>270.19656000000003</v>
+      </c>
+      <c r="BA22" s="2">
+        <f t="shared" si="135"/>
+        <v>243.17690400000004</v>
+      </c>
+      <c r="BB22" s="2">
+        <f t="shared" si="135"/>
+        <v>218.85921360000003</v>
+      </c>
+      <c r="BC22" s="2">
+        <f t="shared" ref="BC22:BG22" si="136">BB22*0.9</f>
+        <v>196.97329224000003</v>
+      </c>
+      <c r="BD22" s="2">
         <f t="shared" si="136"/>
-        <v>283.5</v>
-      </c>
-      <c r="AY22" s="2">
+        <v>177.27596301600005</v>
+      </c>
+      <c r="BE22" s="2">
         <f t="shared" si="136"/>
-        <v>255.15</v>
-      </c>
-      <c r="AZ22" s="2">
+        <v>159.54836671440006</v>
+      </c>
+      <c r="BF22" s="2">
         <f t="shared" si="136"/>
-        <v>229.63500000000002</v>
-      </c>
-      <c r="BA22" s="2">
+        <v>143.59353004296005</v>
+      </c>
+      <c r="BG22" s="2">
         <f t="shared" si="136"/>
-        <v>206.67150000000001</v>
-      </c>
-      <c r="BB22" s="2">
-        <f t="shared" si="136"/>
-        <v>186.00435000000002</v>
-      </c>
-      <c r="BC22" s="2">
-        <f t="shared" ref="BC22:BG22" si="137">BB22*0.9</f>
-        <v>167.40391500000001</v>
-      </c>
-      <c r="BD22" s="2">
-        <f t="shared" si="137"/>
-        <v>150.66352350000003</v>
-      </c>
-      <c r="BE22" s="2">
-        <f t="shared" si="137"/>
-        <v>135.59717115000004</v>
-      </c>
-      <c r="BF22" s="2">
-        <f t="shared" si="137"/>
-        <v>122.03745403500004</v>
-      </c>
-      <c r="BG22" s="2">
-        <f t="shared" si="137"/>
-        <v>109.83370863150003</v>
+        <v>129.23417703866406</v>
       </c>
     </row>
     <row r="23" spans="1:180" x14ac:dyDescent="0.3">
@@ -5208,7 +5198,7 @@
         <v>119</v>
       </c>
       <c r="AJ23" s="1">
-        <v>0</v>
+        <v>-320</v>
       </c>
       <c r="AK23" s="1">
         <v>0</v>
@@ -5218,7 +5208,7 @@
       </c>
       <c r="AM23" s="1"/>
       <c r="AO23" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>125.1</v>
       </c>
       <c r="AP23" s="2">
@@ -5230,7 +5220,7 @@
         <v>-45</v>
       </c>
       <c r="AR23" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>122</v>
       </c>
       <c r="AS23" s="2">
@@ -5250,7 +5240,8 @@
         <v>-695</v>
       </c>
       <c r="AW23" s="2">
-        <v>0</v>
+        <f t="shared" si="127"/>
+        <v>-201</v>
       </c>
       <c r="AX23" s="2">
         <v>0</v>
@@ -5288,152 +5279,152 @@
         <v>17</v>
       </c>
       <c r="C24" s="4">
-        <f t="shared" ref="C24:E24" si="138">C20-C21-C22-C23</f>
+        <f t="shared" ref="C24:E24" si="137">C20-C21-C22-C23</f>
         <v>-371.7</v>
       </c>
       <c r="D24" s="4">
+        <f t="shared" si="137"/>
+        <v>-385.70000000000067</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="137"/>
+        <v>-671.40000000000043</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" ref="F24:I24" si="138">F20-F21-F22-F23</f>
+        <v>-779.69999999999993</v>
+      </c>
+      <c r="G24" s="4">
         <f t="shared" si="138"/>
-        <v>-385.70000000000067</v>
-      </c>
-      <c r="E24" s="4">
+        <v>-778.70000000000027</v>
+      </c>
+      <c r="H24" s="4">
         <f t="shared" si="138"/>
-        <v>-671.40000000000043</v>
-      </c>
-      <c r="F24" s="4">
-        <f t="shared" ref="F24:I24" si="139">F20-F21-F22-F23</f>
-        <v>-779.69999999999993</v>
-      </c>
-      <c r="G24" s="4">
+        <v>-729.29999999999984</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="138"/>
+        <v>270.80000000000126</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" ref="J24:U24" si="139">J20-J21-J22-J23</f>
+        <v>231.90000000000003</v>
+      </c>
+      <c r="K24" s="4">
         <f t="shared" si="139"/>
-        <v>-778.70000000000027</v>
-      </c>
-      <c r="H24" s="4">
+        <v>-645</v>
+      </c>
+      <c r="L24" s="4">
         <f t="shared" si="139"/>
-        <v>-729.29999999999984</v>
-      </c>
-      <c r="I24" s="4">
+        <v>-370</v>
+      </c>
+      <c r="M24" s="4">
         <f t="shared" si="139"/>
-        <v>270.80000000000126</v>
-      </c>
-      <c r="J24" s="4">
-        <f t="shared" ref="J24:U24" si="140">J20-J21-J22-J23</f>
-        <v>231.90000000000003</v>
-      </c>
-      <c r="K24" s="4">
-        <f t="shared" si="140"/>
-        <v>-645</v>
-      </c>
-      <c r="L24" s="4">
-        <f t="shared" si="140"/>
-        <v>-370</v>
-      </c>
-      <c r="M24" s="4">
-        <f t="shared" si="140"/>
         <v>176</v>
       </c>
       <c r="N24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>174</v>
       </c>
       <c r="O24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>70</v>
       </c>
       <c r="P24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>150</v>
       </c>
       <c r="Q24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>555</v>
       </c>
       <c r="R24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>379</v>
       </c>
       <c r="S24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>533</v>
       </c>
       <c r="T24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>1293</v>
       </c>
       <c r="U24" s="4">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>1882</v>
       </c>
       <c r="V24" s="4">
-        <f t="shared" ref="V24" si="141">V20-V21-V22-V23</f>
+        <f t="shared" ref="V24" si="140">V20-V21-V22-V23</f>
         <v>2635</v>
       </c>
       <c r="W24" s="4">
-        <f t="shared" ref="W24" si="142">W20-W21-W22-W23</f>
+        <f t="shared" ref="W24" si="141">W20-W21-W22-W23</f>
         <v>3626</v>
       </c>
       <c r="X24" s="4">
-        <f t="shared" ref="X24" si="143">X20-X21-X22-X23</f>
+        <f t="shared" ref="X24" si="142">X20-X21-X22-X23</f>
         <v>2474</v>
       </c>
       <c r="Y24" s="4">
-        <f t="shared" ref="Y24" si="144">Y20-Y21-Y22-Y23</f>
+        <f t="shared" ref="Y24" si="143">Y20-Y21-Y22-Y23</f>
         <v>3636</v>
       </c>
       <c r="Z24" s="4">
-        <f t="shared" ref="Z24" si="145">Z20-Z21-Z22-Z23</f>
+        <f t="shared" ref="Z24" si="144">Z20-Z21-Z22-Z23</f>
         <v>3983</v>
       </c>
       <c r="AA24" s="4">
-        <f t="shared" ref="AA24" si="146">AA20-AA21-AA22-AA23</f>
+        <f t="shared" ref="AA24" si="145">AA20-AA21-AA22-AA23</f>
         <v>2800</v>
       </c>
       <c r="AB24" s="4">
-        <f t="shared" ref="AB24:AC24" si="147">AB20-AB21-AB22-AB23</f>
+        <f t="shared" ref="AB24:AC24" si="146">AB20-AB21-AB22-AB23</f>
         <v>2937</v>
       </c>
       <c r="AC24" s="4">
+        <f t="shared" si="146"/>
+        <v>2045</v>
+      </c>
+      <c r="AD24" s="4">
+        <f t="shared" ref="AD24:AE24" si="147">AD20-AD21-AD22-AD23</f>
+        <v>2191</v>
+      </c>
+      <c r="AE24" s="4">
         <f t="shared" si="147"/>
-        <v>2045</v>
-      </c>
-      <c r="AD24" s="4">
-        <f t="shared" ref="AD24:AE24" si="148">AD20-AD21-AD22-AD23</f>
-        <v>2191</v>
-      </c>
-      <c r="AE24" s="4">
+        <v>1553</v>
+      </c>
+      <c r="AF24" s="4">
+        <f t="shared" ref="AF24:AL24" si="148">AF20-AF21-AF22-AF23</f>
+        <v>1887</v>
+      </c>
+      <c r="AG24" s="4">
         <f t="shared" si="148"/>
-        <v>1553</v>
-      </c>
-      <c r="AF24" s="4">
-        <f t="shared" ref="AF24:AL24" si="149">AF20-AF21-AF22-AF23</f>
-        <v>1887</v>
-      </c>
-      <c r="AG24" s="4">
-        <f t="shared" si="149"/>
         <v>2784</v>
       </c>
       <c r="AH24" s="4">
-        <f t="shared" si="149"/>
+        <f t="shared" si="148"/>
         <v>2766</v>
       </c>
       <c r="AI24" s="4">
-        <f t="shared" si="149"/>
+        <f t="shared" si="148"/>
         <v>589</v>
       </c>
       <c r="AJ24" s="4">
-        <f t="shared" si="149"/>
-        <v>1363.9834000000005</v>
+        <f t="shared" si="148"/>
+        <v>1549</v>
       </c>
       <c r="AK24" s="4">
-        <f t="shared" si="149"/>
-        <v>1505.9680000000019</v>
+        <f t="shared" si="148"/>
+        <v>885.21000000000129</v>
       </c>
       <c r="AL24" s="4">
-        <f t="shared" si="149"/>
-        <v>1366.482600000003</v>
+        <f t="shared" si="148"/>
+        <v>1043.4352000000017</v>
       </c>
       <c r="AM24" s="4"/>
       <c r="AO24" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-2208.5000000000009</v>
       </c>
       <c r="AP24" s="6">
@@ -5445,7 +5436,7 @@
         <v>-665</v>
       </c>
       <c r="AR24" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>1154</v>
       </c>
       <c r="AS24" s="6">
@@ -5461,52 +5452,52 @@
         <v>9973</v>
       </c>
       <c r="AV24" s="6">
-        <f t="shared" ref="AV24:BG24" si="150">AV20-AV21-AV22-AV23</f>
+        <f t="shared" ref="AV24:BG24" si="149">AV20-AV21-AV22-AV23</f>
         <v>8990</v>
       </c>
       <c r="AW24" s="6">
-        <f t="shared" si="150"/>
-        <v>5730.9765000000198</v>
+        <f t="shared" si="149"/>
+        <v>4066.6452000000031</v>
       </c>
       <c r="AX24" s="6">
-        <f t="shared" si="150"/>
-        <v>10096.158732000007</v>
+        <f t="shared" si="149"/>
+        <v>8552.7081560000261</v>
       </c>
       <c r="AY24" s="6">
-        <f t="shared" si="150"/>
-        <v>11026.30638864</v>
+        <f t="shared" si="149"/>
+        <v>9551.0164211600022</v>
       </c>
       <c r="AZ24" s="6">
-        <f t="shared" si="150"/>
-        <v>12592.822354118818</v>
+        <f t="shared" si="149"/>
+        <v>11373.507821885203</v>
       </c>
       <c r="BA24" s="6">
-        <f t="shared" si="150"/>
-        <v>13951.734008033671</v>
+        <f t="shared" si="149"/>
+        <v>12756.279233450485</v>
       </c>
       <c r="BB24" s="6">
-        <f t="shared" si="150"/>
-        <v>15841.171923772308</v>
+        <f t="shared" si="149"/>
+        <v>14958.020218031565</v>
       </c>
       <c r="BC24" s="6">
-        <f t="shared" si="150"/>
-        <v>17032.244472908536</v>
+        <f t="shared" si="149"/>
+        <v>16179.804678552107</v>
       </c>
       <c r="BD24" s="6">
-        <f t="shared" si="150"/>
-        <v>18807.813214430964</v>
+        <f t="shared" si="149"/>
+        <v>18308.618179905381</v>
       </c>
       <c r="BE24" s="6">
-        <f t="shared" si="150"/>
-        <v>20192.427921747523</v>
+        <f t="shared" si="149"/>
+        <v>19807.580839880025</v>
       </c>
       <c r="BF24" s="6">
-        <f t="shared" si="150"/>
-        <v>22542.663849406901</v>
+        <f t="shared" si="149"/>
+        <v>22636.11174777415</v>
       </c>
       <c r="BG24" s="6">
-        <f t="shared" si="150"/>
-        <v>23990.263734900131</v>
+        <f t="shared" si="149"/>
+        <v>24266.86040168894</v>
       </c>
     </row>
     <row r="25" spans="1:180" x14ac:dyDescent="0.3">
@@ -5613,20 +5604,19 @@
         <v>169</v>
       </c>
       <c r="AJ25" s="1">
-        <f t="shared" ref="AJ25:AL25" si="151">AJ24*0.2</f>
-        <v>272.79668000000009</v>
+        <v>359</v>
       </c>
       <c r="AK25" s="1">
-        <f t="shared" si="151"/>
-        <v>301.1936000000004</v>
+        <f t="shared" ref="AK25:AL25" si="150">AK24*0.2</f>
+        <v>177.04200000000026</v>
       </c>
       <c r="AL25" s="1">
-        <f t="shared" si="151"/>
-        <v>273.29652000000061</v>
+        <f t="shared" si="150"/>
+        <v>208.68704000000037</v>
       </c>
       <c r="AM25" s="1"/>
       <c r="AO25" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>31.5</v>
       </c>
       <c r="AP25" s="2">
@@ -5638,7 +5628,7 @@
         <v>110</v>
       </c>
       <c r="AR25" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>292</v>
       </c>
       <c r="AS25" s="2">
@@ -5658,48 +5648,48 @@
         <v>1837</v>
       </c>
       <c r="AW25" s="2">
-        <f>AW24*0.2</f>
-        <v>1146.195300000004</v>
+        <f t="shared" ref="AW25:AW26" si="151">SUM(AI25:AL25)</f>
+        <v>913.72904000000062</v>
       </c>
       <c r="AX25" s="2">
         <f t="shared" ref="AX25:BG25" si="152">AX24*0.2</f>
-        <v>2019.2317464000016</v>
+        <v>1710.5416312000052</v>
       </c>
       <c r="AY25" s="2">
         <f t="shared" si="152"/>
-        <v>2205.2612777280001</v>
+        <v>1910.2032842320004</v>
       </c>
       <c r="AZ25" s="2">
         <f t="shared" si="152"/>
-        <v>2518.5644708237637</v>
+        <v>2274.7015643770405</v>
       </c>
       <c r="BA25" s="2">
         <f t="shared" si="152"/>
-        <v>2790.3468016067345</v>
+        <v>2551.2558466900973</v>
       </c>
       <c r="BB25" s="2">
         <f t="shared" si="152"/>
-        <v>3168.2343847544616</v>
+        <v>2991.6040436063131</v>
       </c>
       <c r="BC25" s="2">
         <f t="shared" si="152"/>
-        <v>3406.4488945817075</v>
+        <v>3235.9609357104218</v>
       </c>
       <c r="BD25" s="2">
         <f t="shared" si="152"/>
-        <v>3761.5626428861929</v>
+        <v>3661.7236359810763</v>
       </c>
       <c r="BE25" s="2">
         <f t="shared" si="152"/>
-        <v>4038.4855843495047</v>
+        <v>3961.5161679760054</v>
       </c>
       <c r="BF25" s="2">
         <f t="shared" si="152"/>
-        <v>4508.5327698813808</v>
+        <v>4527.2223495548305</v>
       </c>
       <c r="BG25" s="2">
         <f t="shared" si="152"/>
-        <v>4798.0527469800263</v>
+        <v>4853.3720803377882</v>
       </c>
     </row>
     <row r="26" spans="1:180" x14ac:dyDescent="0.3">
@@ -5806,20 +5796,19 @@
         <v>11</v>
       </c>
       <c r="AJ26" s="1">
-        <f t="shared" ref="AJ26:AL26" si="153">AJ24*0.008</f>
-        <v>10.911867200000005</v>
+        <v>18</v>
       </c>
       <c r="AK26" s="1">
-        <f t="shared" si="153"/>
-        <v>12.047744000000016</v>
+        <f t="shared" ref="AK26:AL26" si="153">AK24*0.008</f>
+        <v>7.0816800000000102</v>
       </c>
       <c r="AL26" s="1">
         <f t="shared" si="153"/>
-        <v>10.931860800000024</v>
+        <v>8.3474816000000143</v>
       </c>
       <c r="AM26" s="1"/>
       <c r="AO26" s="2">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-279.10000000000002</v>
       </c>
       <c r="AP26" s="2">
@@ -5831,7 +5820,7 @@
         <v>87</v>
       </c>
       <c r="AR26" s="2">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>143</v>
       </c>
       <c r="AS26" s="2">
@@ -5851,48 +5840,48 @@
         <v>62</v>
       </c>
       <c r="AW26" s="2">
-        <f>AW24*0.01</f>
-        <v>57.309765000000198</v>
+        <f t="shared" si="151"/>
+        <v>44.429161600000029</v>
       </c>
       <c r="AX26" s="2">
         <f t="shared" ref="AX26:BG26" si="154">AX24*0.01</f>
-        <v>100.96158732000008</v>
+        <v>85.527081560000269</v>
       </c>
       <c r="AY26" s="2">
         <f t="shared" si="154"/>
-        <v>110.2630638864</v>
+        <v>95.510164211600028</v>
       </c>
       <c r="AZ26" s="2">
         <f t="shared" si="154"/>
-        <v>125.92822354118819</v>
+        <v>113.73507821885204</v>
       </c>
       <c r="BA26" s="2">
         <f t="shared" si="154"/>
-        <v>139.51734008033671</v>
+        <v>127.56279233450485</v>
       </c>
       <c r="BB26" s="2">
         <f t="shared" si="154"/>
-        <v>158.41171923772308</v>
+        <v>149.58020218031564</v>
       </c>
       <c r="BC26" s="2">
         <f t="shared" si="154"/>
-        <v>170.32244472908536</v>
+        <v>161.79804678552108</v>
       </c>
       <c r="BD26" s="2">
         <f t="shared" si="154"/>
-        <v>188.07813214430965</v>
+        <v>183.0861817990538</v>
       </c>
       <c r="BE26" s="2">
         <f t="shared" si="154"/>
-        <v>201.92427921747523</v>
+        <v>198.07580839880026</v>
       </c>
       <c r="BF26" s="2">
         <f t="shared" si="154"/>
-        <v>225.42663849406901</v>
+        <v>226.36111747774152</v>
       </c>
       <c r="BG26" s="2">
         <f t="shared" si="154"/>
-        <v>239.90263734900131</v>
+        <v>242.66860401688942</v>
       </c>
     </row>
     <row r="27" spans="1:180" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -6033,15 +6022,15 @@
       </c>
       <c r="AJ27" s="4">
         <f t="shared" si="176"/>
-        <v>1080.2748528000004</v>
+        <v>1172</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="176"/>
-        <v>1192.7266560000016</v>
+        <v>701.08632000000102</v>
       </c>
       <c r="AL27" s="4">
         <f t="shared" si="176"/>
-        <v>1082.2542192000024</v>
+        <v>826.40067840000131</v>
       </c>
       <c r="AM27" s="4"/>
       <c r="AO27" s="4">
@@ -6078,531 +6067,531 @@
       </c>
       <c r="AW27" s="4">
         <f t="shared" ref="AW27" si="183">AW24-AW25-AW26</f>
-        <v>4527.4714350000158</v>
+        <v>3108.4869984000024</v>
       </c>
       <c r="AX27" s="4">
         <f t="shared" ref="AX27" si="184">AX24-AX25-AX26</f>
-        <v>7975.9653982800055</v>
+        <v>6756.6394432400202</v>
       </c>
       <c r="AY27" s="4">
         <f t="shared" ref="AY27" si="185">AY24-AY25-AY26</f>
-        <v>8710.7820470256011</v>
+        <v>7545.3029727164021</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" ref="AZ27" si="186">AZ24-AZ25-AZ26</f>
-        <v>9948.3296597538665</v>
+        <v>8985.0711792893107</v>
       </c>
       <c r="BA27" s="4">
         <f t="shared" ref="BA27" si="187">BA24-BA25-BA26</f>
-        <v>11021.8698663466</v>
+        <v>10077.460594425882</v>
       </c>
       <c r="BB27" s="4">
         <f t="shared" ref="BB27:BG27" si="188">BB24-BB25-BB26</f>
-        <v>12514.525819780123</v>
+        <v>11816.835972244937</v>
       </c>
       <c r="BC27" s="4">
         <f t="shared" si="188"/>
-        <v>13455.473133597745</v>
+        <v>12782.045696056164</v>
       </c>
       <c r="BD27" s="4">
         <f t="shared" si="188"/>
-        <v>14858.172439400461</v>
+        <v>14463.808362125252</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="188"/>
-        <v>15952.018058180543</v>
+        <v>15647.988863505219</v>
       </c>
       <c r="BF27" s="4">
         <f t="shared" si="188"/>
-        <v>17808.704441031452</v>
+        <v>17882.528280741579</v>
       </c>
       <c r="BG27" s="4">
         <f t="shared" si="188"/>
-        <v>18952.308350571104</v>
+        <v>19170.819717334263</v>
       </c>
       <c r="BH27" s="3">
         <f t="shared" ref="BH27:CM27" si="189">BG27*(1+$BJ$30)</f>
-        <v>18762.785267065392</v>
+        <v>18979.111520160921</v>
       </c>
       <c r="BI27" s="3">
         <f t="shared" si="189"/>
-        <v>18575.157414394736</v>
+        <v>18789.320404959311</v>
       </c>
       <c r="BJ27" s="3">
         <f t="shared" si="189"/>
-        <v>18389.405840250787</v>
+        <v>18601.427200909719</v>
       </c>
       <c r="BK27" s="3">
         <f t="shared" si="189"/>
-        <v>18205.511781848279</v>
+        <v>18415.41292890062</v>
       </c>
       <c r="BL27" s="3">
         <f t="shared" si="189"/>
-        <v>18023.456664029796</v>
+        <v>18231.258799611613</v>
       </c>
       <c r="BM27" s="3">
         <f t="shared" si="189"/>
-        <v>17843.222097389498</v>
+        <v>18048.946211615497</v>
       </c>
       <c r="BN27" s="3">
         <f t="shared" si="189"/>
-        <v>17664.789876415602</v>
+        <v>17868.456749499343</v>
       </c>
       <c r="BO27" s="3">
         <f t="shared" si="189"/>
-        <v>17488.141977651445</v>
+        <v>17689.772182004348</v>
       </c>
       <c r="BP27" s="3">
         <f t="shared" si="189"/>
-        <v>17313.260557874932</v>
+        <v>17512.874460184303</v>
       </c>
       <c r="BQ27" s="3">
         <f t="shared" si="189"/>
-        <v>17140.127952296181</v>
+        <v>17337.74571558246</v>
       </c>
       <c r="BR27" s="3">
         <f t="shared" si="189"/>
-        <v>16968.72667277322</v>
+        <v>17164.368258426635</v>
       </c>
       <c r="BS27" s="3">
         <f t="shared" si="189"/>
-        <v>16799.039406045489</v>
+        <v>16992.724575842371</v>
       </c>
       <c r="BT27" s="3">
         <f t="shared" si="189"/>
-        <v>16631.049011985033</v>
+        <v>16822.797330083948</v>
       </c>
       <c r="BU27" s="3">
         <f t="shared" si="189"/>
-        <v>16464.738521865183</v>
+        <v>16654.569356783108</v>
       </c>
       <c r="BV27" s="3">
         <f t="shared" si="189"/>
-        <v>16300.091136646532</v>
+        <v>16488.023663215277</v>
       </c>
       <c r="BW27" s="3">
         <f t="shared" si="189"/>
-        <v>16137.090225280066</v>
+        <v>16323.143426583125</v>
       </c>
       <c r="BX27" s="3">
         <f t="shared" si="189"/>
-        <v>15975.719323027266</v>
+        <v>16159.911992317293</v>
       </c>
       <c r="BY27" s="3">
         <f t="shared" si="189"/>
-        <v>15815.962129796993</v>
+        <v>15998.312872394119</v>
       </c>
       <c r="BZ27" s="3">
         <f t="shared" si="189"/>
-        <v>15657.802508499024</v>
+        <v>15838.329743670178</v>
       </c>
       <c r="CA27" s="3">
         <f t="shared" si="189"/>
-        <v>15501.224483414033</v>
+        <v>15679.946446233476</v>
       </c>
       <c r="CB27" s="3">
         <f t="shared" si="189"/>
-        <v>15346.212238579892</v>
+        <v>15523.146981771142</v>
       </c>
       <c r="CC27" s="3">
         <f t="shared" si="189"/>
-        <v>15192.750116194093</v>
+        <v>15367.91551195343</v>
       </c>
       <c r="CD27" s="3">
         <f t="shared" si="189"/>
-        <v>15040.822615032152</v>
+        <v>15214.236356833895</v>
       </c>
       <c r="CE27" s="3">
         <f t="shared" si="189"/>
-        <v>14890.414388881831</v>
+        <v>15062.093993265556</v>
       </c>
       <c r="CF27" s="3">
         <f t="shared" si="189"/>
-        <v>14741.510244993013</v>
+        <v>14911.4730533329</v>
       </c>
       <c r="CG27" s="3">
         <f t="shared" si="189"/>
-        <v>14594.095142543083</v>
+        <v>14762.358322799571</v>
       </c>
       <c r="CH27" s="3">
         <f t="shared" si="189"/>
-        <v>14448.154191117652</v>
+        <v>14614.734739571575</v>
       </c>
       <c r="CI27" s="3">
         <f t="shared" si="189"/>
-        <v>14303.672649206475</v>
+        <v>14468.587392175859</v>
       </c>
       <c r="CJ27" s="3">
         <f t="shared" si="189"/>
-        <v>14160.635922714411</v>
+        <v>14323.901518254101</v>
       </c>
       <c r="CK27" s="3">
         <f t="shared" si="189"/>
-        <v>14019.029563487267</v>
+        <v>14180.66250307156</v>
       </c>
       <c r="CL27" s="3">
         <f t="shared" si="189"/>
-        <v>13878.839267852394</v>
+        <v>14038.855878040844</v>
       </c>
       <c r="CM27" s="3">
         <f t="shared" si="189"/>
-        <v>13740.050875173871</v>
+        <v>13898.467319260435</v>
       </c>
       <c r="CN27" s="3">
         <f t="shared" ref="CN27:DS27" si="190">CM27*(1+$BJ$30)</f>
-        <v>13602.650366422133</v>
+        <v>13759.482646067831</v>
       </c>
       <c r="CO27" s="3">
         <f t="shared" si="190"/>
-        <v>13466.623862757911</v>
+        <v>13621.887819607153</v>
       </c>
       <c r="CP27" s="3">
         <f t="shared" si="190"/>
-        <v>13331.957624130333</v>
+        <v>13485.668941411081</v>
       </c>
       <c r="CQ27" s="3">
         <f t="shared" si="190"/>
-        <v>13198.63804788903</v>
+        <v>13350.812251996969</v>
       </c>
       <c r="CR27" s="3">
         <f t="shared" si="190"/>
-        <v>13066.651667410139</v>
+        <v>13217.304129476999</v>
       </c>
       <c r="CS27" s="3">
         <f t="shared" si="190"/>
-        <v>12935.985150736036</v>
+        <v>13085.131088182228</v>
       </c>
       <c r="CT27" s="3">
         <f t="shared" si="190"/>
-        <v>12806.625299228675</v>
+        <v>12954.279777300406</v>
       </c>
       <c r="CU27" s="3">
         <f t="shared" si="190"/>
-        <v>12678.559046236389</v>
+        <v>12824.736979527401</v>
       </c>
       <c r="CV27" s="3">
         <f t="shared" si="190"/>
-        <v>12551.773455774024</v>
+        <v>12696.489609732127</v>
       </c>
       <c r="CW27" s="3">
         <f t="shared" si="190"/>
-        <v>12426.255721216285</v>
+        <v>12569.524713634806</v>
       </c>
       <c r="CX27" s="3">
         <f t="shared" si="190"/>
-        <v>12301.993164004121</v>
+        <v>12443.829466498459</v>
       </c>
       <c r="CY27" s="3">
         <f t="shared" si="190"/>
-        <v>12178.97323236408</v>
+        <v>12319.391171833475</v>
       </c>
       <c r="CZ27" s="3">
         <f t="shared" si="190"/>
-        <v>12057.183500040439</v>
+        <v>12196.197260115139</v>
       </c>
       <c r="DA27" s="3">
         <f t="shared" si="190"/>
-        <v>11936.611665040034</v>
+        <v>12074.235287513988</v>
       </c>
       <c r="DB27" s="3">
         <f t="shared" si="190"/>
-        <v>11817.245548389634</v>
+        <v>11953.492934638847</v>
       </c>
       <c r="DC27" s="3">
         <f t="shared" si="190"/>
-        <v>11699.073092905737</v>
+        <v>11833.958005292459</v>
       </c>
       <c r="DD27" s="3">
         <f t="shared" si="190"/>
-        <v>11582.08236197668</v>
+        <v>11715.618425239534</v>
       </c>
       <c r="DE27" s="3">
         <f t="shared" si="190"/>
-        <v>11466.261538356914</v>
+        <v>11598.462240987139</v>
       </c>
       <c r="DF27" s="3">
         <f t="shared" si="190"/>
-        <v>11351.598922973344</v>
+        <v>11482.477618577268</v>
       </c>
       <c r="DG27" s="3">
         <f t="shared" si="190"/>
-        <v>11238.08293374361</v>
+        <v>11367.652842391495</v>
       </c>
       <c r="DH27" s="3">
         <f t="shared" si="190"/>
-        <v>11125.702104406173</v>
+        <v>11253.97631396758</v>
       </c>
       <c r="DI27" s="3">
         <f t="shared" si="190"/>
-        <v>11014.44508336211</v>
+        <v>11141.436550827904</v>
       </c>
       <c r="DJ27" s="3">
         <f t="shared" si="190"/>
-        <v>10904.30063252849</v>
+        <v>11030.022185319625</v>
       </c>
       <c r="DK27" s="3">
         <f t="shared" si="190"/>
-        <v>10795.257626203205</v>
+        <v>10919.721963466429</v>
       </c>
       <c r="DL27" s="3">
         <f t="shared" si="190"/>
-        <v>10687.305049941173</v>
+        <v>10810.524743831764</v>
       </c>
       <c r="DM27" s="3">
         <f t="shared" si="190"/>
-        <v>10580.431999441762</v>
+        <v>10702.419496393446</v>
       </c>
       <c r="DN27" s="3">
         <f t="shared" si="190"/>
-        <v>10474.627679447343</v>
+        <v>10595.395301429511</v>
       </c>
       <c r="DO27" s="3">
         <f t="shared" si="190"/>
-        <v>10369.881402652869</v>
+        <v>10489.441348415216</v>
       </c>
       <c r="DP27" s="3">
         <f t="shared" si="190"/>
-        <v>10266.18258862634</v>
+        <v>10384.546934931062</v>
       </c>
       <c r="DQ27" s="3">
         <f t="shared" si="190"/>
-        <v>10163.520762740076</v>
+        <v>10280.701465581751</v>
       </c>
       <c r="DR27" s="3">
         <f t="shared" si="190"/>
-        <v>10061.885555112674</v>
+        <v>10177.894450925933</v>
       </c>
       <c r="DS27" s="3">
         <f t="shared" si="190"/>
-        <v>9961.2666995615473</v>
+        <v>10076.115506416674</v>
       </c>
       <c r="DT27" s="3">
         <f t="shared" ref="DT27:EY27" si="191">DS27*(1+$BJ$30)</f>
-        <v>9861.6540325659316</v>
+        <v>9975.3543513525074</v>
       </c>
       <c r="DU27" s="3">
         <f t="shared" si="191"/>
-        <v>9763.0374922402716</v>
+        <v>9875.6008078389823</v>
       </c>
       <c r="DV27" s="3">
         <f t="shared" si="191"/>
-        <v>9665.4071173178691</v>
+        <v>9776.8447997605927</v>
       </c>
       <c r="DW27" s="3">
         <f t="shared" si="191"/>
-        <v>9568.7530461446895</v>
+        <v>9679.0763517629875</v>
       </c>
       <c r="DX27" s="3">
         <f t="shared" si="191"/>
-        <v>9473.0655156832418</v>
+        <v>9582.2855882453568</v>
       </c>
       <c r="DY27" s="3">
         <f t="shared" si="191"/>
-        <v>9378.3348605264091</v>
+        <v>9486.4627323629029</v>
       </c>
       <c r="DZ27" s="3">
         <f t="shared" si="191"/>
-        <v>9284.551511921145</v>
+        <v>9391.5981050392729</v>
       </c>
       <c r="EA27" s="3">
         <f t="shared" si="191"/>
-        <v>9191.705996801933</v>
+        <v>9297.6821239888795</v>
       </c>
       <c r="EB27" s="3">
         <f t="shared" si="191"/>
-        <v>9099.7889368339129</v>
+        <v>9204.705302748991</v>
       </c>
       <c r="EC27" s="3">
         <f t="shared" si="191"/>
-        <v>9008.7910474655728</v>
+        <v>9112.6582497215004</v>
       </c>
       <c r="ED27" s="3">
         <f t="shared" si="191"/>
-        <v>8918.7031369909164</v>
+        <v>9021.5316672242861</v>
       </c>
       <c r="EE27" s="3">
         <f t="shared" si="191"/>
-        <v>8829.5161056210072</v>
+        <v>8931.3163505520424</v>
       </c>
       <c r="EF27" s="3">
         <f t="shared" si="191"/>
-        <v>8741.2209445647968</v>
+        <v>8842.0031870465227</v>
       </c>
       <c r="EG27" s="3">
         <f t="shared" si="191"/>
-        <v>8653.808735119148</v>
+        <v>8753.5831551760566</v>
       </c>
       <c r="EH27" s="3">
         <f t="shared" si="191"/>
-        <v>8567.2706477679567</v>
+        <v>8666.047323624296</v>
       </c>
       <c r="EI27" s="3">
         <f t="shared" si="191"/>
-        <v>8481.5979412902761</v>
+        <v>8579.3868503880531</v>
       </c>
       <c r="EJ27" s="3">
         <f t="shared" si="191"/>
-        <v>8396.7819618773738</v>
+        <v>8493.5929818841723</v>
       </c>
       <c r="EK27" s="3">
         <f t="shared" si="191"/>
-        <v>8312.8141422585995</v>
+        <v>8408.6570520653313</v>
       </c>
       <c r="EL27" s="3">
         <f t="shared" si="191"/>
-        <v>8229.6860008360127</v>
+        <v>8324.570481544677</v>
       </c>
       <c r="EM27" s="3">
         <f t="shared" si="191"/>
-        <v>8147.3891408276522</v>
+        <v>8241.3247767292305</v>
       </c>
       <c r="EN27" s="3">
         <f t="shared" si="191"/>
-        <v>8065.9152494193759</v>
+        <v>8158.9115289619385</v>
       </c>
       <c r="EO27" s="3">
         <f t="shared" si="191"/>
-        <v>7985.2560969251817</v>
+        <v>8077.3224136723193</v>
       </c>
       <c r="EP27" s="3">
         <f t="shared" si="191"/>
-        <v>7905.4035359559302</v>
+        <v>7996.5491895355963</v>
       </c>
       <c r="EQ27" s="3">
         <f t="shared" si="191"/>
-        <v>7826.3495005963705</v>
+        <v>7916.5836976402406</v>
       </c>
       <c r="ER27" s="3">
         <f t="shared" si="191"/>
-        <v>7748.0860055904068</v>
+        <v>7837.4178606638379</v>
       </c>
       <c r="ES27" s="3">
         <f t="shared" si="191"/>
-        <v>7670.6051455345023</v>
+        <v>7759.0436820571995</v>
       </c>
       <c r="ET27" s="3">
         <f t="shared" si="191"/>
-        <v>7593.8990940791573</v>
+        <v>7681.4532452366275</v>
       </c>
       <c r="EU27" s="3">
         <f t="shared" si="191"/>
-        <v>7517.9601031383654</v>
+        <v>7604.6387127842609</v>
       </c>
       <c r="EV27" s="3">
         <f t="shared" si="191"/>
-        <v>7442.7805021069817</v>
+        <v>7528.5923256564183</v>
       </c>
       <c r="EW27" s="3">
         <f t="shared" si="191"/>
-        <v>7368.352697085912</v>
+        <v>7453.3064023998541</v>
       </c>
       <c r="EX27" s="3">
         <f t="shared" si="191"/>
-        <v>7294.669170115053</v>
+        <v>7378.773338375855</v>
       </c>
       <c r="EY27" s="3">
         <f t="shared" si="191"/>
-        <v>7221.7224784139025</v>
+        <v>7304.9856049920963</v>
       </c>
       <c r="EZ27" s="3">
         <f t="shared" ref="EZ27:FX27" si="192">EY27*(1+$BJ$30)</f>
-        <v>7149.5052536297635</v>
+        <v>7231.9357489421755</v>
       </c>
       <c r="FA27" s="3">
         <f t="shared" si="192"/>
-        <v>7078.0102010934661</v>
+        <v>7159.6163914527533</v>
       </c>
       <c r="FB27" s="3">
         <f t="shared" si="192"/>
-        <v>7007.2300990825315</v>
+        <v>7088.0202275382253</v>
       </c>
       <c r="FC27" s="3">
         <f t="shared" si="192"/>
-        <v>6937.1577980917064</v>
+        <v>7017.1400252628428</v>
       </c>
       <c r="FD27" s="3">
         <f t="shared" si="192"/>
-        <v>6867.7862201107891</v>
+        <v>6946.9686250102141</v>
       </c>
       <c r="FE27" s="3">
         <f t="shared" si="192"/>
-        <v>6799.1083579096812</v>
+        <v>6877.4989387601117</v>
       </c>
       <c r="FF27" s="3">
         <f t="shared" si="192"/>
-        <v>6731.1172743305842</v>
+        <v>6808.723949372511</v>
       </c>
       <c r="FG27" s="3">
         <f t="shared" si="192"/>
-        <v>6663.8061015872781</v>
+        <v>6740.636709878786</v>
       </c>
       <c r="FH27" s="3">
         <f t="shared" si="192"/>
-        <v>6597.1680405714051</v>
+        <v>6673.230342779998</v>
       </c>
       <c r="FI27" s="3">
         <f t="shared" si="192"/>
-        <v>6531.1963601656907</v>
+        <v>6606.4980393521982</v>
       </c>
       <c r="FJ27" s="3">
         <f t="shared" si="192"/>
-        <v>6465.8843965640335</v>
+        <v>6540.4330589586762</v>
       </c>
       <c r="FK27" s="3">
         <f t="shared" si="192"/>
-        <v>6401.2255525983928</v>
+        <v>6475.0287283690895</v>
       </c>
       <c r="FL27" s="3">
         <f t="shared" si="192"/>
-        <v>6337.2132970724087</v>
+        <v>6410.2784410853983</v>
       </c>
       <c r="FM27" s="3">
         <f t="shared" si="192"/>
-        <v>6273.8411641016846</v>
+        <v>6346.1756566745444</v>
       </c>
       <c r="FN27" s="3">
         <f t="shared" si="192"/>
-        <v>6211.1027524606679</v>
+        <v>6282.7139001077985</v>
       </c>
       <c r="FO27" s="3">
         <f t="shared" si="192"/>
-        <v>6148.9917249360615</v>
+        <v>6219.8867611067208</v>
       </c>
       <c r="FP27" s="3">
         <f t="shared" si="192"/>
-        <v>6087.5018076867009</v>
+        <v>6157.687893495654</v>
       </c>
       <c r="FQ27" s="3">
         <f t="shared" si="192"/>
-        <v>6026.6267896098334</v>
+        <v>6096.1110145606972</v>
       </c>
       <c r="FR27" s="3">
         <f t="shared" si="192"/>
-        <v>5966.3605217137347</v>
+        <v>6035.1499044150905</v>
       </c>
       <c r="FS27" s="3">
         <f t="shared" si="192"/>
-        <v>5906.6969164965976</v>
+        <v>5974.7984053709397</v>
       </c>
       <c r="FT27" s="3">
         <f t="shared" si="192"/>
-        <v>5847.6299473316312</v>
+        <v>5915.0504213172298</v>
       </c>
       <c r="FU27" s="3">
         <f t="shared" si="192"/>
-        <v>5789.1536478583148</v>
+        <v>5855.8999171040577</v>
       </c>
       <c r="FV27" s="3">
         <f t="shared" si="192"/>
-        <v>5731.2621113797313</v>
+        <v>5797.3409179330174</v>
       </c>
       <c r="FW27" s="3">
         <f t="shared" si="192"/>
-        <v>5673.9494902659344</v>
+        <v>5739.3675087536876</v>
       </c>
       <c r="FX27" s="3">
         <f t="shared" si="192"/>
-        <v>5617.2099953632751</v>
+        <v>5681.9738336661503</v>
       </c>
     </row>
     <row r="28" spans="1:180" x14ac:dyDescent="0.3">
@@ -6713,16 +6702,13 @@
         <v>3221</v>
       </c>
       <c r="AJ28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="AK28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="AL28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="AM28" s="1"/>
       <c r="AO28" s="2">
@@ -6753,48 +6739,37 @@
         <v>3198</v>
       </c>
       <c r="AW28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="AX28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="AY28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="AZ28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BA28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BB28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BC28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BD28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BE28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BF28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
       <c r="BG28" s="2">
-        <f>3221</f>
-        <v>3221</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="29" spans="1:180" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -6935,15 +6910,15 @@
       </c>
       <c r="AJ29" s="5">
         <f t="shared" si="207"/>
-        <v>0.33538492791058688</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="AK29" s="5">
         <f t="shared" si="207"/>
-        <v>0.37029700589878972</v>
+        <v>0.21752600682593889</v>
       </c>
       <c r="AL29" s="5">
         <f t="shared" si="207"/>
-        <v>0.33599944712822177</v>
+        <v>0.25640728464163864</v>
       </c>
       <c r="AM29" s="5"/>
       <c r="AO29" s="5">
@@ -6980,47 +6955,47 @@
       </c>
       <c r="AW29" s="5">
         <f t="shared" si="208"/>
-        <v>1.4056105045017124</v>
+        <v>0.96447005845485645</v>
       </c>
       <c r="AX29" s="5">
         <f t="shared" ref="AX29:BB29" si="210">AX27/AX28</f>
-        <v>2.4762388693821813</v>
+        <v>2.0963820798138442</v>
       </c>
       <c r="AY29" s="5">
         <f t="shared" si="210"/>
-        <v>2.7043719487816209</v>
+        <v>2.3410806617177791</v>
       </c>
       <c r="AZ29" s="5">
         <f t="shared" si="210"/>
-        <v>3.0885841849592879</v>
+        <v>2.7877974493606299</v>
       </c>
       <c r="BA29" s="5">
         <f t="shared" si="210"/>
-        <v>3.4218782571706301</v>
+        <v>3.1267330420185795</v>
       </c>
       <c r="BB29" s="5">
         <f t="shared" si="210"/>
-        <v>3.8852920893449623</v>
+        <v>3.6664089271625619</v>
       </c>
       <c r="BC29" s="5">
         <f t="shared" ref="BC29:BG29" si="211">BC27/BC28</f>
-        <v>4.1774210287481353</v>
+        <v>3.965884485279604</v>
       </c>
       <c r="BD29" s="5">
         <f t="shared" si="211"/>
-        <v>4.6129066871780386</v>
+        <v>4.4876848781027778</v>
       </c>
       <c r="BE29" s="5">
         <f t="shared" si="211"/>
-        <v>4.9525048302330159</v>
+        <v>4.8551004851086628</v>
       </c>
       <c r="BF29" s="5">
         <f t="shared" si="211"/>
-        <v>5.5289364920929689</v>
+        <v>5.548410884499404</v>
       </c>
       <c r="BG29" s="5">
         <f t="shared" si="211"/>
-        <v>5.8839827229342143</v>
+        <v>5.9481289845902152</v>
       </c>
     </row>
     <row r="30" spans="1:180" x14ac:dyDescent="0.3">
@@ -7158,7 +7133,7 @@
       </c>
       <c r="AJ31" s="9">
         <f t="shared" ref="AJ31:AJ33" si="214">AJ3/AF3-1</f>
-        <v>-0.25</v>
+        <v>-0.14803022126281706</v>
       </c>
       <c r="AK31" s="9">
         <f t="shared" ref="AK31:AK33" si="215">AK3/AG3-1</f>
@@ -7166,7 +7141,7 @@
       </c>
       <c r="AL31" s="9">
         <f t="shared" ref="AL31:AL33" si="216">AL3/AH3-1</f>
-        <v>-0.15000000000000002</v>
+        <v>-0.11999999999999988</v>
       </c>
       <c r="AM31" s="7"/>
       <c r="AN31" s="8"/>
@@ -7201,47 +7176,47 @@
       </c>
       <c r="AW31" s="9">
         <f t="shared" si="217"/>
-        <v>-0.20326365894039733</v>
+        <v>-0.16947130242825603</v>
       </c>
       <c r="AX31" s="9">
         <f t="shared" si="217"/>
-        <v>2.0000000000000018E-2</v>
+        <v>0.15000000000000013</v>
       </c>
       <c r="AY31" s="9">
         <f t="shared" si="217"/>
-        <v>2.0000000000000018E-2</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AZ31" s="9">
         <f t="shared" si="217"/>
-        <v>2.0000000000000018E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="BA31" s="9">
         <f t="shared" si="217"/>
-        <v>2.0000000000000018E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="BB31" s="9">
         <f t="shared" si="217"/>
-        <v>1.0000000000000009E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="BC31" s="9">
         <f t="shared" si="217"/>
-        <v>1.0000000000000009E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BD31" s="9">
         <f t="shared" si="217"/>
-        <v>1.0000000000000009E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE31" s="9">
         <f t="shared" si="217"/>
-        <v>1.0000000000000009E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BF31" s="9">
         <f t="shared" si="217"/>
-        <v>1.0000000000000009E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BG31" s="9">
         <f t="shared" si="217"/>
-        <v>1.0000000000000009E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="BI31" t="s">
         <v>48</v>
@@ -7326,15 +7301,15 @@
       </c>
       <c r="AJ32" s="9">
         <f t="shared" si="214"/>
-        <v>-0.25</v>
+        <v>-0.50674157303370793</v>
       </c>
       <c r="AK32" s="9">
         <f t="shared" si="215"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.25</v>
       </c>
       <c r="AL32" s="9">
         <f t="shared" si="216"/>
-        <v>-0.15000000000000013</v>
+        <v>-0.25</v>
       </c>
       <c r="AM32" s="7"/>
       <c r="AN32" s="8"/>
@@ -7354,54 +7329,54 @@
       </c>
       <c r="AW32" s="9">
         <f t="shared" si="219"/>
-        <v>-0.11621425986246825</v>
+        <v>-0.23733260948244661</v>
       </c>
       <c r="AX32" s="9">
         <f t="shared" si="219"/>
-        <v>5.0000000000000044E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="AY32" s="9">
         <f t="shared" si="219"/>
-        <v>3.0000000000000027E-2</v>
+        <v>-0.19999999999999984</v>
       </c>
       <c r="AZ32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BA32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BB32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999984</v>
       </c>
       <c r="BC32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BD32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BE32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BF32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BG32" s="9">
         <f t="shared" si="219"/>
-        <v>2.0000000000000018E-2</v>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="BI32" s="8" t="s">
         <v>49</v>
       </c>
       <c r="BJ32" s="15">
         <f>NPV(BJ31,AW27:FX27)</f>
-        <v>279834.91867094114</v>
+        <v>275655.59066414007</v>
       </c>
     </row>
     <row r="33" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7530,7 +7505,7 @@
       </c>
       <c r="AJ33" s="9">
         <f t="shared" si="214"/>
-        <v>-5.0000000000000044E-2</v>
+        <v>-5.0218340611353662E-2</v>
       </c>
       <c r="AK33" s="9">
         <f t="shared" si="215"/>
@@ -7570,7 +7545,7 @@
       </c>
       <c r="AW33" s="9">
         <f t="shared" si="221"/>
-        <v>-5.2846195949644348E-2</v>
+        <v>-5.2900930487137399E-2</v>
       </c>
       <c r="AX33" s="9">
         <f t="shared" si="221"/>
@@ -7578,11 +7553,11 @@
       </c>
       <c r="AY33" s="9">
         <f t="shared" si="221"/>
-        <v>-5.0000000000000044E-2</v>
+        <v>-5.0000000000000155E-2</v>
       </c>
       <c r="AZ33" s="9">
         <f t="shared" si="221"/>
-        <v>-5.0000000000000044E-2</v>
+        <v>-5.0000000000000155E-2</v>
       </c>
       <c r="BA33" s="9">
         <f t="shared" si="221"/>
@@ -7602,11 +7577,11 @@
       </c>
       <c r="BE33" s="9">
         <f t="shared" si="221"/>
-        <v>-4.9999999999999933E-2</v>
+        <v>-5.0000000000000044E-2</v>
       </c>
       <c r="BF33" s="9">
         <f t="shared" si="221"/>
-        <v>-4.9999999999999933E-2</v>
+        <v>-5.0000000000000044E-2</v>
       </c>
       <c r="BG33" s="9">
         <f t="shared" si="221"/>
@@ -7617,7 +7592,7 @@
       </c>
       <c r="BJ33" s="15">
         <f>Main!D8</f>
-        <v>29467</v>
+        <v>29562</v>
       </c>
     </row>
     <row r="34" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7746,7 +7721,7 @@
       </c>
       <c r="AJ34" s="9">
         <f t="shared" ref="AJ34:AJ36" si="251">AJ7/AF7-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <v>-7.4651625746516292E-2</v>
       </c>
       <c r="AK34" s="9">
         <f t="shared" ref="AK34:AK36" si="252">AK7/AG7-1</f>
@@ -7786,7 +7761,7 @@
       </c>
       <c r="AW34" s="9">
         <f t="shared" si="254"/>
-        <v>0.18236664683720005</v>
+        <v>0.1660350981558596</v>
       </c>
       <c r="AX34" s="9">
         <f t="shared" si="254"/>
@@ -7833,7 +7808,7 @@
       </c>
       <c r="BJ34" s="15">
         <f>BJ32+BJ33</f>
-        <v>309301.91867094114</v>
+        <v>305217.59066414007</v>
       </c>
     </row>
     <row r="35" spans="1:62" s="8" customFormat="1" x14ac:dyDescent="0.3">
@@ -7962,7 +7937,7 @@
       </c>
       <c r="AJ35" s="9">
         <f t="shared" si="251"/>
-        <v>0.10000000000000009</v>
+        <v>0.16794478527607359</v>
       </c>
       <c r="AK35" s="9">
         <f t="shared" si="252"/>
@@ -8004,7 +7979,7 @@
       </c>
       <c r="AW35" s="9">
         <f t="shared" si="256"/>
-        <v>0.11150560091133488</v>
+        <v>0.12832732105562927</v>
       </c>
       <c r="AX35" s="9">
         <f t="shared" si="256"/>
@@ -8051,7 +8026,7 @@
       </c>
       <c r="BJ35" s="10">
         <f>BJ34/BB28</f>
-        <v>96.026674533045991</v>
+        <v>94.69984196839593</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -8181,15 +8156,15 @@
       </c>
       <c r="AJ36" s="7">
         <f t="shared" si="251"/>
-        <v>-0.18342666666666674</v>
+        <v>-0.1178039215686274</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="252"/>
-        <v>-0.1169287586371216</v>
+        <v>-0.11839607656262396</v>
       </c>
       <c r="AL36" s="7">
         <f t="shared" si="253"/>
-        <v>-9.9131364997860461E-2</v>
+        <v>-8.0048235889057406E-2</v>
       </c>
       <c r="AM36" s="8"/>
       <c r="AO36" s="8"/>
@@ -8223,54 +8198,54 @@
       </c>
       <c r="AW36" s="7">
         <f t="shared" si="258"/>
-        <v>-0.12423226532910214</v>
+        <v>-0.10245931006244247</v>
       </c>
       <c r="AX36" s="7">
         <f t="shared" si="258"/>
-        <v>7.6261023041070519E-2</v>
+        <v>0.157760962354907</v>
       </c>
       <c r="AY36" s="7">
         <f t="shared" si="258"/>
-        <v>7.6763514888190221E-2</v>
+        <v>0.11509337641351292</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="258"/>
-        <v>7.4382652282634965E-2</v>
+        <v>9.8184712188718937E-2</v>
       </c>
       <c r="BA36" s="7">
         <f t="shared" si="258"/>
-        <v>7.7495964539447737E-2</v>
+        <v>8.6897450549551225E-2</v>
       </c>
       <c r="BB36" s="7">
         <f t="shared" si="258"/>
-        <v>6.5846189846399783E-2</v>
+        <v>7.4927303848950189E-2</v>
       </c>
       <c r="BC36" s="7">
         <f t="shared" si="258"/>
-        <v>5.9017087229659371E-2</v>
+        <v>6.2632762113461027E-2</v>
       </c>
       <c r="BD36" s="7">
         <f t="shared" si="258"/>
-        <v>6.4296257857373584E-2</v>
+        <v>6.6872427916434329E-2</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="258"/>
-        <v>6.9976319599411863E-2</v>
+        <v>7.1381635456011727E-2</v>
       </c>
       <c r="BF36" s="7">
         <f t="shared" si="258"/>
-        <v>7.6032955207299135E-2</v>
+        <v>7.6173006461905945E-2</v>
       </c>
       <c r="BG36" s="7">
         <f t="shared" si="258"/>
-        <v>8.2428122374777146E-2</v>
+        <v>8.1247347281973248E-2</v>
       </c>
       <c r="BI36" s="8" t="s">
         <v>54</v>
       </c>
       <c r="BJ36" s="10">
         <f>Main!D3</f>
-        <v>348.37</v>
+        <v>312.60000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8337,7 +8312,7 @@
       </c>
       <c r="BJ37" s="16">
         <f>BJ35/BJ36-1</f>
-        <v>-0.72435435160017803</v>
+        <v>-0.69705744731799135</v>
       </c>
     </row>
     <row r="38" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8478,7 +8453,7 @@
       </c>
       <c r="AJ38" s="9">
         <f t="shared" si="260"/>
-        <v>0.11000000000000003</v>
+        <v>0.14062203078482297</v>
       </c>
       <c r="AK38" s="9">
         <f t="shared" si="260"/>
@@ -8486,7 +8461,7 @@
       </c>
       <c r="AL38" s="9">
         <f t="shared" si="260"/>
-        <v>0.11000000000000001</v>
+        <v>0.13000000000000006</v>
       </c>
       <c r="AM38" s="7"/>
       <c r="AO38"/>
@@ -8520,47 +8495,47 @@
       </c>
       <c r="AW38" s="9">
         <f t="shared" si="261"/>
-        <v>0.11073163403752037</v>
+        <v>0.12418812187773692</v>
       </c>
       <c r="AX38" s="9">
         <f t="shared" si="261"/>
-        <v>0.16000000000000003</v>
+        <v>0.16000000000000009</v>
       </c>
       <c r="AY38" s="9">
         <f t="shared" si="261"/>
-        <v>0.16000000000000006</v>
+        <v>0.16000000000000003</v>
       </c>
       <c r="AZ38" s="9">
         <f t="shared" si="261"/>
-        <v>0.17000000000000007</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="BA38" s="9">
         <f t="shared" si="261"/>
-        <v>0.17000000000000007</v>
+        <v>0.17000000000000004</v>
       </c>
       <c r="BB38" s="9">
         <f t="shared" si="261"/>
-        <v>0.18000000000000002</v>
+        <v>0.18000000000000013</v>
       </c>
       <c r="BC38" s="9">
         <f t="shared" si="261"/>
-        <v>0.18000000000000005</v>
+        <v>0.1800000000000001</v>
       </c>
       <c r="BD38" s="9">
         <f t="shared" si="261"/>
-        <v>0.18999999999999997</v>
+        <v>0.19</v>
       </c>
       <c r="BE38" s="9">
         <f t="shared" si="261"/>
-        <v>0.18999999999999997</v>
+        <v>0.18999999999999995</v>
       </c>
       <c r="BF38" s="9">
         <f t="shared" si="261"/>
-        <v>0.19999999999999993</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="BG38" s="9">
         <f t="shared" si="261"/>
-        <v>0.19999999999999993</v>
+        <v>0.2</v>
       </c>
       <c r="BI38" t="s">
         <v>64</v>
@@ -8707,7 +8682,7 @@
       </c>
       <c r="AJ39" s="9">
         <f t="shared" si="263"/>
-        <v>0.47000000000000003</v>
+        <v>0.47586206896551725</v>
       </c>
       <c r="AK39" s="9">
         <f t="shared" si="263"/>
@@ -8749,7 +8724,7 @@
       </c>
       <c r="AW39" s="9">
         <f t="shared" si="264"/>
-        <v>0.46879222167644252</v>
+        <v>0.47026584217065903</v>
       </c>
       <c r="AX39" s="9">
         <f t="shared" si="264"/>
@@ -8757,11 +8732,11 @@
       </c>
       <c r="AY39" s="9">
         <f t="shared" si="264"/>
-        <v>0.46</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="AZ39" s="9">
         <f t="shared" si="264"/>
-        <v>0.45999999999999996</v>
+        <v>0.45999999999999991</v>
       </c>
       <c r="BA39" s="9">
         <f t="shared" si="264"/>
@@ -8769,11 +8744,11 @@
       </c>
       <c r="BB39" s="9">
         <f t="shared" si="264"/>
-        <v>0.46</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BC39" s="9">
         <f t="shared" si="264"/>
-        <v>0.45999999999999991</v>
+        <v>0.46</v>
       </c>
       <c r="BD39" s="9">
         <f t="shared" si="264"/>
@@ -8785,11 +8760,11 @@
       </c>
       <c r="BF39" s="9">
         <f t="shared" si="264"/>
-        <v>0.46</v>
+        <v>0.45999999999999996</v>
       </c>
       <c r="BG39" s="9">
         <f t="shared" si="264"/>
-        <v>0.45999999999999996</v>
+        <v>0.45999999999999991</v>
       </c>
     </row>
     <row r="40" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -8930,7 +8905,7 @@
       </c>
       <c r="AJ40" s="9">
         <f t="shared" si="266"/>
-        <v>0.26999999999999996</v>
+        <v>0.30333452850484044</v>
       </c>
       <c r="AK40" s="9">
         <f t="shared" si="266"/>
@@ -8972,19 +8947,19 @@
       </c>
       <c r="AW40" s="9">
         <f t="shared" si="267"/>
-        <v>0.27401665359926547</v>
+        <v>0.28197809981268002</v>
       </c>
       <c r="AX40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AY40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AZ40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3000000000000001</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="BA40" s="9">
         <f t="shared" si="267"/>
@@ -8992,11 +8967,11 @@
       </c>
       <c r="BB40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3000000000000001</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="BC40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3</v>
+        <v>0.3000000000000001</v>
       </c>
       <c r="BD40" s="9">
         <f t="shared" si="267"/>
@@ -9004,15 +8979,15 @@
       </c>
       <c r="BE40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3000000000000001</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="BF40" s="9">
         <f t="shared" si="267"/>
-        <v>0.3000000000000001</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="BG40" s="9">
         <f t="shared" si="267"/>
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="41" spans="1:62" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -9153,7 +9128,7 @@
       </c>
       <c r="AJ41" s="9">
         <f t="shared" si="269"/>
-        <v>6.0000000000000053E-2</v>
+        <v>5.4497701904136574E-2</v>
       </c>
       <c r="AK41" s="9">
         <f t="shared" si="269"/>
@@ -9195,19 +9170,19 @@
       </c>
       <c r="AW41" s="9">
         <f t="shared" si="270"/>
-        <v>5.5107869429308426E-2</v>
+        <v>5.3770717999629673E-2</v>
       </c>
       <c r="AX41" s="9">
         <f t="shared" si="270"/>
-        <v>6.0000000000000053E-2</v>
+        <v>6.0000000000000095E-2</v>
       </c>
       <c r="AY41" s="9">
         <f t="shared" si="270"/>
-        <v>6.0000000000000109E-2</v>
+        <v>6.0000000000000039E-2</v>
       </c>
       <c r="AZ41" s="9">
         <f t="shared" si="270"/>
-        <v>6.000000000000013E-2</v>
+        <v>5.9999999999999977E-2</v>
       </c>
       <c r="BA41" s="9">
         <f t="shared" si="270"/>
@@ -9219,11 +9194,11 @@
       </c>
       <c r="BC41" s="9">
         <f t="shared" si="270"/>
-        <v>0.11999999999999998</v>
+        <v>0.11999999999999994</v>
       </c>
       <c r="BD41" s="9">
         <f t="shared" si="270"/>
-        <v>0.13000000000000003</v>
+        <v>0.13000000000000006</v>
       </c>
       <c r="BE41" s="9">
         <f t="shared" si="270"/>
@@ -9231,11 +9206,11 @@
       </c>
       <c r="BF41" s="9">
         <f t="shared" si="270"/>
-        <v>0.15000000000000008</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="BG41" s="9">
         <f t="shared" si="270"/>
-        <v>0.15000000000000002</v>
+        <v>0.15000000000000005</v>
       </c>
       <c r="BI41"/>
       <c r="BJ41"/>
@@ -9379,15 +9354,15 @@
       </c>
       <c r="AJ42" s="7">
         <f t="shared" si="274"/>
-        <v>0.16186024621301259</v>
+        <v>0.17238620199146515</v>
       </c>
       <c r="AK42" s="7">
         <f t="shared" si="274"/>
-        <v>0.15584409218662179</v>
+        <v>0.15443910173396611</v>
       </c>
       <c r="AL42" s="7">
         <f t="shared" si="274"/>
-        <v>0.15422475768212554</v>
+        <v>0.16458938145899232</v>
       </c>
       <c r="AM42" s="8"/>
       <c r="AO42" s="7">
@@ -9424,47 +9399,47 @@
       </c>
       <c r="AW42" s="7">
         <f t="shared" si="275"/>
-        <v>0.15850353140569545</v>
+        <v>0.16368518973662979</v>
       </c>
       <c r="AX42" s="7">
         <f t="shared" ref="AX42:BB42" si="276">AX15/AX9</f>
-        <v>0.19769469877530635</v>
+        <v>0.18642794689776271</v>
       </c>
       <c r="AY42" s="7">
         <f t="shared" si="276"/>
-        <v>0.19884601145454045</v>
+        <v>0.1838963876771641</v>
       </c>
       <c r="AZ42" s="7">
         <f t="shared" si="276"/>
-        <v>0.20501957712563265</v>
+        <v>0.18865158950673366</v>
       </c>
       <c r="BA42" s="7">
         <f t="shared" si="276"/>
-        <v>0.20696417910917403</v>
+        <v>0.18925301221344371</v>
       </c>
       <c r="BB42" s="7">
         <f t="shared" si="276"/>
-        <v>0.21393697334375553</v>
+        <v>0.19611106140779666</v>
       </c>
       <c r="BC42" s="7">
         <f t="shared" ref="BC42:BG42" si="277">BC15/BC9</f>
-        <v>0.21520162543345753</v>
+        <v>0.196783402768169</v>
       </c>
       <c r="BD42" s="7">
         <f t="shared" si="277"/>
-        <v>0.21930069770531907</v>
+        <v>0.20186378681727379</v>
       </c>
       <c r="BE42" s="7">
         <f t="shared" si="277"/>
-        <v>0.21880310035343925</v>
+        <v>0.20157224414110378</v>
       </c>
       <c r="BF42" s="7">
         <f t="shared" si="277"/>
-        <v>0.22285016269534907</v>
+        <v>0.207043647748899</v>
       </c>
       <c r="BG42" s="7">
         <f t="shared" si="277"/>
-        <v>0.21925608993093873</v>
+        <v>0.2044542105513007</v>
       </c>
       <c r="BI42" t="s">
         <v>62</v>
@@ -9596,15 +9571,15 @@
       </c>
       <c r="AJ43" s="9">
         <f t="shared" ref="AJ43" si="296">AJ16/AF16-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.47951582867783982</v>
       </c>
       <c r="AK43" s="9">
         <f t="shared" ref="AK43" si="297">AK16/AG16-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.5</v>
       </c>
       <c r="AL43" s="9">
         <f t="shared" ref="AL43" si="298">AL16/AH16-1</f>
-        <v>0.10000000000000009</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="AM43" s="9"/>
       <c r="AN43" s="3"/>
@@ -9639,7 +9614,7 @@
       </c>
       <c r="AW43" s="9">
         <f t="shared" si="299"/>
-        <v>9.000000000000008E-2</v>
+        <v>0.39711453744493386</v>
       </c>
       <c r="AX43" s="9">
         <f t="shared" si="299"/>
@@ -9820,15 +9795,15 @@
       </c>
       <c r="AJ44" s="9">
         <f t="shared" si="301"/>
-        <v>5.000000000000001E-2</v>
+        <v>6.0721906116642958E-2</v>
       </c>
       <c r="AK44" s="9">
         <f t="shared" si="301"/>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AL44" s="9">
         <f t="shared" si="301"/>
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="AM44" s="8"/>
       <c r="AO44" s="9">
@@ -9865,7 +9840,7 @@
       </c>
       <c r="AW44" s="9">
         <f t="shared" si="302"/>
-        <v>5.2000000000000005E-2</v>
+        <v>6.1221932978447385E-2</v>
       </c>
       <c r="AX44" s="9">
         <f t="shared" si="302"/>
@@ -9901,7 +9876,7 @@
       </c>
       <c r="BF44" s="9">
         <f t="shared" si="302"/>
-        <v>5.1999999999999998E-2</v>
+        <v>5.1999999999999991E-2</v>
       </c>
       <c r="BG44" s="9">
         <f t="shared" ref="BG44" si="303">BG17/BG9</f>
@@ -10046,15 +10021,15 @@
       </c>
       <c r="AJ45" s="16">
         <f t="shared" si="305"/>
-        <v>5.2544943911957305E-2</v>
+        <v>4.1029516358463726E-2</v>
       </c>
       <c r="AK45" s="16">
         <f t="shared" si="305"/>
-        <v>5.2112782462057416E-2</v>
+        <v>2.4238138244322829E-2</v>
       </c>
       <c r="AL45" s="16">
         <f t="shared" si="305"/>
-        <v>4.3616681988528805E-2</v>
+        <v>2.9051942560424943E-2</v>
       </c>
       <c r="AM45" s="7"/>
       <c r="AN45" s="3"/>
@@ -10092,47 +10067,47 @@
       </c>
       <c r="AW45" s="16">
         <f t="shared" si="306"/>
-        <v>4.866153149335966E-2</v>
+        <v>2.9050335449913499E-2</v>
       </c>
       <c r="AX45" s="16">
         <f t="shared" si="306"/>
-        <v>8.8189187954779771E-2</v>
+        <v>6.7570700698828048E-2</v>
       </c>
       <c r="AY45" s="16">
         <f t="shared" si="306"/>
-        <v>9.0769829891290899E-2</v>
+        <v>6.8941921267663256E-2</v>
       </c>
       <c r="AZ45" s="16">
         <f t="shared" si="306"/>
-        <v>9.8737959024414748E-2</v>
+        <v>7.7032616178110552E-2</v>
       </c>
       <c r="BA45" s="16">
         <f t="shared" si="306"/>
-        <v>0.10307529183324632</v>
+        <v>8.0755002674978732E-2</v>
       </c>
       <c r="BB45" s="16">
         <f t="shared" si="306"/>
-        <v>0.11179319612397894</v>
+        <v>8.9974423873100423E-2</v>
       </c>
       <c r="BC45" s="16">
         <f t="shared" si="306"/>
-        <v>0.11443178861101407</v>
+        <v>9.2309266219023758E-2</v>
       </c>
       <c r="BD45" s="16">
         <f t="shared" si="306"/>
-        <v>0.12010243729966377</v>
+        <v>9.9203221194470878E-2</v>
       </c>
       <c r="BE45" s="16">
         <f t="shared" si="306"/>
-        <v>0.12136825536918237</v>
+        <v>0.10086842015845962</v>
       </c>
       <c r="BF45" s="16">
         <f t="shared" si="306"/>
-        <v>0.12735903158517883</v>
+        <v>0.10842945244674318</v>
       </c>
       <c r="BG45" s="16">
         <f t="shared" si="306"/>
-        <v>0.12587148053517017</v>
+        <v>0.10804936527522759</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -10273,7 +10248,7 @@
       </c>
       <c r="AJ46" s="9">
         <f t="shared" si="310"/>
-        <v>0.19999999999999998</v>
+        <v>0.23176242737249839</v>
       </c>
       <c r="AK46" s="9">
         <f t="shared" si="310"/>
@@ -10318,7 +10293,7 @@
       </c>
       <c r="AW46" s="9">
         <f t="shared" si="311"/>
-        <v>0.2</v>
+        <v>0.22468865491388329</v>
       </c>
       <c r="AX46" s="9">
         <f t="shared" si="311"/>
@@ -10330,7 +10305,7 @@
       </c>
       <c r="AZ46" s="9">
         <f t="shared" si="311"/>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="BA46" s="9">
         <f t="shared" si="311"/>
@@ -10499,7 +10474,7 @@
       </c>
       <c r="AJ47" s="9">
         <f t="shared" si="316"/>
-        <v>8.0000000000000002E-3</v>
+        <v>1.1620400258231117E-2</v>
       </c>
       <c r="AK47" s="9">
         <f t="shared" si="316"/>
@@ -10543,7 +10518,7 @@
       </c>
       <c r="AW47" s="9">
         <f t="shared" si="317"/>
-        <v>0.01</v>
+        <v>1.0925261343182826E-2</v>
       </c>
       <c r="AX47" s="9">
         <f t="shared" si="317"/>
@@ -10724,15 +10699,15 @@
       </c>
       <c r="AJ48" s="9">
         <f t="shared" si="320"/>
-        <v>5.1879871639591964E-2</v>
+        <v>5.209815078236131E-2</v>
       </c>
       <c r="AK48" s="9">
         <f t="shared" si="320"/>
-        <v>5.3635824890387922E-2</v>
+        <v>3.1579682485343874E-2</v>
       </c>
       <c r="AL48" s="9">
         <f t="shared" si="320"/>
-        <v>4.6732221171977888E-2</v>
+        <v>3.4944128274952274E-2</v>
       </c>
       <c r="AO48" s="9">
         <f t="shared" ref="AO48:BG48" si="321">AO27/AO9</f>
@@ -10768,47 +10743,47 @@
       </c>
       <c r="AW48" s="9">
         <f t="shared" si="321"/>
-        <v>5.2919614102245841E-2</v>
+        <v>3.5452331308753658E-2</v>
       </c>
       <c r="AX48" s="9">
         <f t="shared" si="321"/>
-        <v>8.6621679182545458E-2</v>
+        <v>6.655912228804961E-2</v>
       </c>
       <c r="AY48" s="9">
         <f t="shared" si="321"/>
-        <v>8.7857765389737844E-2</v>
+        <v>6.6656466705468514E-2</v>
       </c>
       <c r="AZ48" s="9">
         <f t="shared" si="321"/>
-        <v>9.33929699670938E-2</v>
+        <v>7.2278933258469791E-2</v>
       </c>
       <c r="BA48" s="9">
         <f t="shared" si="321"/>
-        <v>9.6029273913976851E-2</v>
+        <v>7.4585215857652196E-2</v>
       </c>
       <c r="BB48" s="9">
         <f t="shared" si="321"/>
-        <v>0.10229825549687624</v>
+        <v>8.1362400819596364E-2</v>
       </c>
       <c r="BC48" s="9">
         <f t="shared" si="321"/>
-        <v>0.10386036271434564</v>
+        <v>8.2820855497830984E-2</v>
       </c>
       <c r="BD48" s="9">
         <f t="shared" si="321"/>
-        <v>0.10775904174109149</v>
+        <v>8.7843476267355974E-2</v>
       </c>
       <c r="BE48" s="9">
         <f t="shared" si="321"/>
-        <v>0.1081259143119669</v>
+        <v>8.8703587666253345E-2</v>
       </c>
       <c r="BF48" s="9">
         <f t="shared" si="321"/>
-        <v>0.11218141510057719</v>
+        <v>9.4195354122743546E-2</v>
       </c>
       <c r="BG48" s="9">
         <f t="shared" si="321"/>
-        <v>0.11029393573507265</v>
+        <v>9.3393400967627049E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/TSLA.xlsx
+++ b/Financial Analysis/TSLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E56FCAE-8AF6-4337-A3FE-8B242BCCC30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDF737C-3C78-4153-A7DF-EC6BCB4865C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -848,7 +848,7 @@
       </c>
       <c r="F3" s="11">
         <f ca="1">TODAY()</f>
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="G3" s="11">
         <v>46140</v>
